--- a/GOA CEATTLE/Model runs/GOA_25/Results/GOA 2025 Cod ESP Indices.xlsx
+++ b/GOA CEATTLE/Model runs/GOA_25/Results/GOA 2025 Cod ESP Indices.xlsx
@@ -379,7 +379,7 @@
         <v>1977</v>
       </c>
       <c r="B2">
-        <v>0.6284151043186949</v>
+        <v>0.6284140835672848</v>
       </c>
       <c r="C2">
         <v>0.492942</v>
@@ -390,7 +390,7 @@
         <v>1978</v>
       </c>
       <c r="B3">
-        <v>0.6055655017446814</v>
+        <v>0.6055639886084474</v>
       </c>
       <c r="C3">
         <v>0.492942</v>
@@ -401,7 +401,7 @@
         <v>1979</v>
       </c>
       <c r="B4">
-        <v>0.5810800795377679</v>
+        <v>0.5810784784267289</v>
       </c>
       <c r="C4">
         <v>0.492942</v>
@@ -412,7 +412,7 @@
         <v>1980</v>
       </c>
       <c r="B5">
-        <v>0.5801987748253998</v>
+        <v>0.5801971771023227</v>
       </c>
       <c r="C5">
         <v>0.492942</v>
@@ -423,7 +423,7 @@
         <v>1981</v>
       </c>
       <c r="B6">
-        <v>0.6094202491528143</v>
+        <v>0.6094188651830434</v>
       </c>
       <c r="C6">
         <v>0.492942</v>
@@ -434,7 +434,7 @@
         <v>1982</v>
       </c>
       <c r="B7">
-        <v>0.5958563951376403</v>
+        <v>0.5958546103890016</v>
       </c>
       <c r="C7">
         <v>0.492942</v>
@@ -445,7 +445,7 @@
         <v>1983</v>
       </c>
       <c r="B8">
-        <v>0.6270338068403758</v>
+        <v>0.6270325007028805</v>
       </c>
       <c r="C8">
         <v>0.492942</v>
@@ -456,7 +456,7 @@
         <v>1984</v>
       </c>
       <c r="B9">
-        <v>0.6267308349518055</v>
+        <v>0.6267295912662285</v>
       </c>
       <c r="C9">
         <v>0.492942</v>
@@ -467,7 +467,7 @@
         <v>1985</v>
       </c>
       <c r="B10">
-        <v>0.6178438736611934</v>
+        <v>0.6178424903436113</v>
       </c>
       <c r="C10">
         <v>0.492942</v>
@@ -478,7 +478,7 @@
         <v>1986</v>
       </c>
       <c r="B11">
-        <v>0.6174970985456409</v>
+        <v>0.6174956352175619</v>
       </c>
       <c r="C11">
         <v>0.492942</v>
@@ -489,7 +489,7 @@
         <v>1987</v>
       </c>
       <c r="B12">
-        <v>0.6267540172031866</v>
+        <v>0.6267526773497661</v>
       </c>
       <c r="C12">
         <v>0.492942</v>
@@ -500,7 +500,7 @@
         <v>1988</v>
       </c>
       <c r="B13">
-        <v>0.6241494347118329</v>
+        <v>0.6241479675925681</v>
       </c>
       <c r="C13">
         <v>0.492942</v>
@@ -511,7 +511,7 @@
         <v>1989</v>
       </c>
       <c r="B14">
-        <v>0.6491742212153416</v>
+        <v>0.6491728290140465</v>
       </c>
       <c r="C14">
         <v>0.492942</v>
@@ -522,7 +522,7 @@
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>0.6838365142825638</v>
+        <v>0.6838355412701718</v>
       </c>
       <c r="C15">
         <v>0.492942</v>
@@ -533,7 +533,7 @@
         <v>1991</v>
       </c>
       <c r="B16">
-        <v>0.7109010135441963</v>
+        <v>0.7109006942161671</v>
       </c>
       <c r="C16">
         <v>0.492942</v>
@@ -544,7 +544,7 @@
         <v>1992</v>
       </c>
       <c r="B17">
-        <v>0.7594586009373456</v>
+        <v>0.7594594124613165</v>
       </c>
       <c r="C17">
         <v>0.492942</v>
@@ -555,7 +555,7 @@
         <v>1993</v>
       </c>
       <c r="B18">
-        <v>0.7799210804671317</v>
+        <v>0.7799228759140893</v>
       </c>
       <c r="C18">
         <v>0.492942</v>
@@ -566,7 +566,7 @@
         <v>1994</v>
       </c>
       <c r="B19">
-        <v>0.7881409020264347</v>
+        <v>0.7881432871604723</v>
       </c>
       <c r="C19">
         <v>0.492942</v>
@@ -577,7 +577,7 @@
         <v>1995</v>
       </c>
       <c r="B20">
-        <v>0.7504201878771278</v>
+        <v>0.7504218314441791</v>
       </c>
       <c r="C20">
         <v>0.492942</v>
@@ -588,7 +588,7 @@
         <v>1996</v>
       </c>
       <c r="B21">
-        <v>0.7558686673210622</v>
+        <v>0.7558704198910935</v>
       </c>
       <c r="C21">
         <v>0.492942</v>
@@ -599,7 +599,7 @@
         <v>1997</v>
       </c>
       <c r="B22">
-        <v>0.7261276574376561</v>
+        <v>0.7261289654637684</v>
       </c>
       <c r="C22">
         <v>0.492942</v>
@@ -610,7 +610,7 @@
         <v>1998</v>
       </c>
       <c r="B23">
-        <v>0.7255636701923805</v>
+        <v>0.7255649235667551</v>
       </c>
       <c r="C23">
         <v>0.492942</v>
@@ -621,7 +621,7 @@
         <v>1999</v>
       </c>
       <c r="B24">
-        <v>0.6672589186205934</v>
+        <v>0.6672590720847671</v>
       </c>
       <c r="C24">
         <v>0.492942</v>
@@ -632,7 +632,7 @@
         <v>2000</v>
       </c>
       <c r="B25">
-        <v>0.6616916045222768</v>
+        <v>0.6616915710805069</v>
       </c>
       <c r="C25">
         <v>0.492942</v>
@@ -643,7 +643,7 @@
         <v>2001</v>
       </c>
       <c r="B26">
-        <v>0.6918209041314192</v>
+        <v>0.6918211432633512</v>
       </c>
       <c r="C26">
         <v>0.492942</v>
@@ -654,7 +654,7 @@
         <v>2002</v>
       </c>
       <c r="B27">
-        <v>0.7324118191999665</v>
+        <v>0.7324126954392047</v>
       </c>
       <c r="C27">
         <v>0.492942</v>
@@ -665,7 +665,7 @@
         <v>2003</v>
       </c>
       <c r="B28">
-        <v>0.8352859608409906</v>
+        <v>0.8352885547983013</v>
       </c>
       <c r="C28">
         <v>0.492942</v>
@@ -676,7 +676,7 @@
         <v>2004</v>
       </c>
       <c r="B29">
-        <v>0.8616987654203115</v>
+        <v>0.8617015110392654</v>
       </c>
       <c r="C29">
         <v>0.492942</v>
@@ -687,7 +687,7 @@
         <v>2005</v>
       </c>
       <c r="B30">
-        <v>0.8686587407268918</v>
+        <v>0.8686613912856289</v>
       </c>
       <c r="C30">
         <v>0.492942</v>
@@ -698,7 +698,7 @@
         <v>2006</v>
       </c>
       <c r="B31">
-        <v>0.7755549082453439</v>
+        <v>0.7755561003814908</v>
       </c>
       <c r="C31">
         <v>0.492942</v>
@@ -709,7 +709,7 @@
         <v>2007</v>
       </c>
       <c r="B32">
-        <v>0.7100019227411438</v>
+        <v>0.7100022361171351</v>
       </c>
       <c r="C32">
         <v>0.492942</v>
@@ -720,7 +720,7 @@
         <v>2008</v>
       </c>
       <c r="B33">
-        <v>0.6933694090895304</v>
+        <v>0.6933696938983973</v>
       </c>
       <c r="C33">
         <v>0.492942</v>
@@ -731,7 +731,7 @@
         <v>2009</v>
       </c>
       <c r="B34">
-        <v>0.6862035444177919</v>
+        <v>0.6862038835983684</v>
       </c>
       <c r="C34">
         <v>0.492942</v>
@@ -742,7 +742,7 @@
         <v>2010</v>
       </c>
       <c r="B35">
-        <v>0.7440561325323323</v>
+        <v>0.7440572318200878</v>
       </c>
       <c r="C35">
         <v>0.492942</v>
@@ -753,7 +753,7 @@
         <v>2011</v>
       </c>
       <c r="B36">
-        <v>0.6954419306202256</v>
+        <v>0.6954419696588554</v>
       </c>
       <c r="C36">
         <v>0.492942</v>
@@ -764,7 +764,7 @@
         <v>2012</v>
       </c>
       <c r="B37">
-        <v>0.6442710406852243</v>
+        <v>0.6442700961351459</v>
       </c>
       <c r="C37">
         <v>0.492942</v>
@@ -775,7 +775,7 @@
         <v>2013</v>
       </c>
       <c r="B38">
-        <v>0.59616939073007</v>
+        <v>0.5961678972730829</v>
       </c>
       <c r="C38">
         <v>0.492942</v>
@@ -786,7 +786,7 @@
         <v>2014</v>
       </c>
       <c r="B39">
-        <v>0.5666914952416111</v>
+        <v>0.5666895851419369</v>
       </c>
       <c r="C39">
         <v>0.492942</v>
@@ -797,7 +797,7 @@
         <v>2015</v>
       </c>
       <c r="B40">
-        <v>0.6215448108308164</v>
+        <v>0.6215436604262268</v>
       </c>
       <c r="C40">
         <v>0.492942</v>
@@ -808,7 +808,7 @@
         <v>2016</v>
       </c>
       <c r="B41">
-        <v>0.6527461010776622</v>
+        <v>0.6527455197701554</v>
       </c>
       <c r="C41">
         <v>0.492942</v>
@@ -819,7 +819,7 @@
         <v>2017</v>
       </c>
       <c r="B42">
-        <v>0.651791205038969</v>
+        <v>0.651790650396957</v>
       </c>
       <c r="C42">
         <v>0.492942</v>
@@ -830,7 +830,7 @@
         <v>2018</v>
       </c>
       <c r="B43">
-        <v>0.6468266225078882</v>
+        <v>0.6468260629513092</v>
       </c>
       <c r="C43">
         <v>0.492942</v>
@@ -841,7 +841,7 @@
         <v>2019</v>
       </c>
       <c r="B44">
-        <v>0.6451199762017398</v>
+        <v>0.6451194452751847</v>
       </c>
       <c r="C44">
         <v>0.492942</v>
@@ -852,7 +852,7 @@
         <v>2020</v>
       </c>
       <c r="B45">
-        <v>0.6168336005666833</v>
+        <v>0.6168326010412801</v>
       </c>
       <c r="C45">
         <v>0.492942</v>
@@ -863,7 +863,7 @@
         <v>2021</v>
       </c>
       <c r="B46">
-        <v>0.6241028888989441</v>
+        <v>0.6241020927754963</v>
       </c>
       <c r="C46">
         <v>0.492942</v>
@@ -874,7 +874,7 @@
         <v>2022</v>
       </c>
       <c r="B47">
-        <v>0.6756151614040399</v>
+        <v>0.6756152978355653</v>
       </c>
       <c r="C47">
         <v>0.492942</v>
@@ -885,7 +885,7 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>0.6756566064064392</v>
+        <v>0.675656890162969</v>
       </c>
       <c r="C48">
         <v>0.492942</v>
@@ -896,7 +896,7 @@
         <v>2024</v>
       </c>
       <c r="B49">
-        <v>0.6725218669654973</v>
+        <v>0.6725222887713093</v>
       </c>
       <c r="C49">
         <v>0.492942</v>
@@ -907,7 +907,7 @@
         <v>2025</v>
       </c>
       <c r="B50">
-        <v>0.6694728823639807</v>
+        <v>0.6694732253316422</v>
       </c>
       <c r="C50">
         <v>0.492942</v>
@@ -955,16 +955,16 @@
         <v>1977</v>
       </c>
       <c r="B2">
-        <v>170355.8410831577</v>
+        <v>170355.8451649182</v>
       </c>
       <c r="C2">
-        <v>68375.57831954057</v>
+        <v>68375.58069949184</v>
       </c>
       <c r="D2">
-        <v>123456.4414401147</v>
+        <v>123453.376096715</v>
       </c>
       <c r="E2">
-        <v>52852.12876955155</v>
+        <v>52850.91533467436</v>
       </c>
     </row>
     <row r="3">
@@ -972,16 +972,16 @@
         <v>1978</v>
       </c>
       <c r="B3">
-        <v>208094.8149707926</v>
+        <v>208094.8159726218</v>
       </c>
       <c r="C3">
-        <v>83775.9386850648</v>
+        <v>83775.94120782787</v>
       </c>
       <c r="D3">
-        <v>152462.3380326519</v>
+        <v>152458.707245448</v>
       </c>
       <c r="E3">
-        <v>65538.19595907946</v>
+        <v>65536.84331409552</v>
       </c>
     </row>
     <row r="4">
@@ -989,16 +989,16 @@
         <v>1979</v>
       </c>
       <c r="B4">
-        <v>277564.4415665129</v>
+        <v>277564.4355834289</v>
       </c>
       <c r="C4">
-        <v>87517.25828034845</v>
+        <v>87517.25986196386</v>
       </c>
       <c r="D4">
-        <v>193615.7321932426</v>
+        <v>193610.7881161118</v>
       </c>
       <c r="E4">
-        <v>68407.22799045645</v>
+        <v>68405.83532874168</v>
       </c>
     </row>
     <row r="5">
@@ -1006,16 +1006,16 @@
         <v>1980</v>
       </c>
       <c r="B5">
-        <v>360857.8924853249</v>
+        <v>360857.8833958529</v>
       </c>
       <c r="C5">
-        <v>91141.03497347955</v>
+        <v>91141.03506761891</v>
       </c>
       <c r="D5">
-        <v>245611.9683119384</v>
+        <v>245605.4321402864</v>
       </c>
       <c r="E5">
-        <v>70106.62693255526</v>
+        <v>70105.14896214393</v>
       </c>
     </row>
     <row r="6">
@@ -1023,16 +1023,16 @@
         <v>1981</v>
       </c>
       <c r="B6">
-        <v>432104.301457724</v>
+        <v>432104.3000389746</v>
       </c>
       <c r="C6">
-        <v>118189.9395013173</v>
+        <v>118189.9352754393</v>
       </c>
       <c r="D6">
-        <v>285438.9955199814</v>
+        <v>285430.6639260004</v>
       </c>
       <c r="E6">
-        <v>83018.98866467946</v>
+        <v>83016.77739171802</v>
       </c>
     </row>
     <row r="7">
@@ -1040,16 +1040,16 @@
         <v>1982</v>
       </c>
       <c r="B7">
-        <v>518319.0357959062</v>
+        <v>518319.0524307973</v>
       </c>
       <c r="C7">
-        <v>167547.808111002</v>
+        <v>167547.8018594395</v>
       </c>
       <c r="D7">
-        <v>332318.9364049247</v>
+        <v>332308.4891887475</v>
       </c>
       <c r="E7">
-        <v>113825.8571680413</v>
+        <v>113822.5884027702</v>
       </c>
     </row>
     <row r="8">
@@ -1057,16 +1057,16 @@
         <v>1983</v>
       </c>
       <c r="B8">
-        <v>616439.9759474701</v>
+        <v>616440.0048275426</v>
       </c>
       <c r="C8">
-        <v>207740.9057258856</v>
+        <v>207740.906764982</v>
       </c>
       <c r="D8">
-        <v>392134.8688061286</v>
+        <v>392122.28550243</v>
       </c>
       <c r="E8">
-        <v>139699.8306686984</v>
+        <v>139695.6639350592</v>
       </c>
     </row>
     <row r="9">
@@ -1074,16 +1074,16 @@
         <v>1984</v>
       </c>
       <c r="B9">
-        <v>689852.0230155899</v>
+        <v>689852.0452638831</v>
       </c>
       <c r="C9">
-        <v>252457.4190668507</v>
+        <v>252457.4327605183</v>
       </c>
       <c r="D9">
-        <v>438998.782184881</v>
+        <v>438984.6381660886</v>
       </c>
       <c r="E9">
-        <v>166414.2216315009</v>
+        <v>166408.9694800796</v>
       </c>
     </row>
     <row r="10">
@@ -1091,16 +1091,16 @@
         <v>1985</v>
       </c>
       <c r="B10">
-        <v>758608.6724569522</v>
+        <v>758608.6730064449</v>
       </c>
       <c r="C10">
-        <v>319723.1242795188</v>
+        <v>319723.1428735273</v>
       </c>
       <c r="D10">
-        <v>494658.6291598117</v>
+        <v>494643.5097955115</v>
       </c>
       <c r="E10">
-        <v>213955.189934841</v>
+        <v>213948.7473759039</v>
       </c>
     </row>
     <row r="11">
@@ -1108,16 +1108,16 @@
         <v>1986</v>
       </c>
       <c r="B11">
-        <v>841091.5507506692</v>
+        <v>841091.5336569843</v>
       </c>
       <c r="C11">
-        <v>381218.137158006</v>
+        <v>381218.1476070861</v>
       </c>
       <c r="D11">
-        <v>566481.0275027269</v>
+        <v>566465.1575254014</v>
       </c>
       <c r="E11">
-        <v>264487.6191652937</v>
+        <v>264480.425644753</v>
       </c>
     </row>
     <row r="12">
@@ -1125,16 +1125,16 @@
         <v>1987</v>
       </c>
       <c r="B12">
-        <v>913968.8888330426</v>
+        <v>913968.8701709966</v>
       </c>
       <c r="C12">
-        <v>413257.3830690506</v>
+        <v>413257.3777888571</v>
       </c>
       <c r="D12">
-        <v>631843.4280047659</v>
+        <v>631827.1056667196</v>
       </c>
       <c r="E12">
-        <v>295129.4541860299</v>
+        <v>295122.0387516835</v>
       </c>
     </row>
     <row r="13">
@@ -1142,16 +1142,16 @@
         <v>1988</v>
       </c>
       <c r="B13">
-        <v>950840.139317906</v>
+        <v>950840.1383330314</v>
       </c>
       <c r="C13">
-        <v>434121.3552015842</v>
+        <v>434121.3388751178</v>
       </c>
       <c r="D13">
-        <v>675518.5251629523</v>
+        <v>675502.4838552753</v>
       </c>
       <c r="E13">
-        <v>316638.8052754456</v>
+        <v>316631.4075348905</v>
       </c>
     </row>
     <row r="14">
@@ -1159,16 +1159,16 @@
         <v>1989</v>
       </c>
       <c r="B14">
-        <v>966425.2200489158</v>
+        <v>966425.2444101907</v>
       </c>
       <c r="C14">
-        <v>472492.0701886445</v>
+        <v>472492.0568402593</v>
       </c>
       <c r="D14">
-        <v>707123.7904735197</v>
+        <v>707108.5305950048</v>
       </c>
       <c r="E14">
-        <v>354125.6331912187</v>
+        <v>354118.1866663951</v>
       </c>
     </row>
     <row r="15">
@@ -1176,16 +1176,16 @@
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>953347.0250964765</v>
+        <v>953347.0646082277</v>
       </c>
       <c r="C15">
-        <v>491124.6839679647</v>
+        <v>491124.6878920327</v>
       </c>
       <c r="D15">
-        <v>716562.4215467088</v>
+        <v>716548.2440173216</v>
       </c>
       <c r="E15">
-        <v>379058.4441277995</v>
+        <v>379051.3313060856</v>
       </c>
     </row>
     <row r="16">
@@ -1193,16 +1193,16 @@
         <v>1991</v>
       </c>
       <c r="B16">
-        <v>910155.828586358</v>
+        <v>910155.8603740599</v>
       </c>
       <c r="C16">
-        <v>466795.693036209</v>
+        <v>466795.7130986929</v>
       </c>
       <c r="D16">
-        <v>694742.9309809242</v>
+        <v>694729.7842816157</v>
       </c>
       <c r="E16">
-        <v>366500.5648557886</v>
+        <v>366494.1373693832</v>
       </c>
     </row>
     <row r="17">
@@ -1210,16 +1210,16 @@
         <v>1992</v>
       </c>
       <c r="B17">
-        <v>871561.617042581</v>
+        <v>871561.6270050883</v>
       </c>
       <c r="C17">
-        <v>433093.5365473961</v>
+        <v>433093.5585982004</v>
       </c>
       <c r="D17">
-        <v>670921.1132971555</v>
+        <v>670908.8010834244</v>
       </c>
       <c r="E17">
-        <v>344828.1182787381</v>
+        <v>344822.3921494451</v>
       </c>
     </row>
     <row r="18">
@@ -1227,16 +1227,16 @@
         <v>1993</v>
       </c>
       <c r="B18">
-        <v>824512.1069965544</v>
+        <v>824512.1024796707</v>
       </c>
       <c r="C18">
-        <v>397862.6581345919</v>
+        <v>397862.6648418929</v>
       </c>
       <c r="D18">
-        <v>639472.6370975726</v>
+        <v>639461.1988868817</v>
       </c>
       <c r="E18">
-        <v>319102.007965281</v>
+        <v>319096.8343379032</v>
       </c>
     </row>
     <row r="19">
@@ -1244,16 +1244,16 @@
         <v>1994</v>
       </c>
       <c r="B19">
-        <v>788570.150391628</v>
+        <v>788570.1557362371</v>
       </c>
       <c r="C19">
-        <v>397400.0679766642</v>
+        <v>397400.0600327513</v>
       </c>
       <c r="D19">
-        <v>623113.963222169</v>
+        <v>623103.647618031</v>
       </c>
       <c r="E19">
-        <v>323921.6183544589</v>
+        <v>323916.7538712264</v>
       </c>
     </row>
     <row r="20">
@@ -1261,16 +1261,16 @@
         <v>1995</v>
       </c>
       <c r="B20">
-        <v>743806.6042696241</v>
+        <v>743806.6326502513</v>
       </c>
       <c r="C20">
-        <v>400246.640556652</v>
+        <v>400246.6332443527</v>
       </c>
       <c r="D20">
-        <v>601383.4120837313</v>
+        <v>601374.4556151127</v>
       </c>
       <c r="E20">
-        <v>334111.1414863749</v>
+        <v>334106.6854439075</v>
       </c>
     </row>
     <row r="21">
@@ -1278,16 +1278,16 @@
         <v>1996</v>
       </c>
       <c r="B21">
-        <v>675103.1684212112</v>
+        <v>675103.2143649874</v>
       </c>
       <c r="C21">
-        <v>365332.3474053784</v>
+        <v>365332.3560466953</v>
       </c>
       <c r="D21">
-        <v>554240.5241225363</v>
+        <v>554232.7971432594</v>
       </c>
       <c r="E21">
-        <v>309752.9991241773</v>
+        <v>309749.1976607979</v>
       </c>
     </row>
     <row r="22">
@@ -1295,16 +1295,16 @@
         <v>1997</v>
       </c>
       <c r="B22">
-        <v>621099.5416795735</v>
+        <v>621099.5865022992</v>
       </c>
       <c r="C22">
-        <v>322134.4669286727</v>
+        <v>322134.4907932275</v>
       </c>
       <c r="D22">
-        <v>513288.6277983173</v>
+        <v>513281.8105393018</v>
       </c>
       <c r="E22">
-        <v>276963.7082306856</v>
+        <v>276960.58625243</v>
       </c>
     </row>
     <row r="23">
@@ -1312,16 +1312,16 @@
         <v>1998</v>
       </c>
       <c r="B23">
-        <v>563529.7076254279</v>
+        <v>563529.7369183403</v>
       </c>
       <c r="C23">
-        <v>273598.1873457416</v>
+        <v>273598.2121637312</v>
       </c>
       <c r="D23">
-        <v>466156.0312040878</v>
+        <v>466149.9774324647</v>
       </c>
       <c r="E23">
-        <v>236556.859796911</v>
+        <v>236554.3043527266</v>
       </c>
     </row>
     <row r="24">
@@ -1329,16 +1329,16 @@
         <v>1999</v>
       </c>
       <c r="B24">
-        <v>510592.9708795593</v>
+        <v>510592.9844316684</v>
       </c>
       <c r="C24">
-        <v>244397.7415356096</v>
+        <v>244397.753735947</v>
       </c>
       <c r="D24">
-        <v>422937.6742138976</v>
+        <v>422932.3223102922</v>
       </c>
       <c r="E24">
-        <v>211353.4757946777</v>
+        <v>211351.2621731538</v>
       </c>
     </row>
     <row r="25">
@@ -1346,16 +1346,16 @@
         <v>2000</v>
       </c>
       <c r="B25">
-        <v>450906.7479542035</v>
+        <v>450906.7563134849</v>
       </c>
       <c r="C25">
-        <v>214631.0709120859</v>
+        <v>214631.0707948864</v>
       </c>
       <c r="D25">
-        <v>372516.561275503</v>
+        <v>372511.7348123892</v>
       </c>
       <c r="E25">
-        <v>183803.059482622</v>
+        <v>183801.0467062579</v>
       </c>
     </row>
     <row r="26">
@@ -1363,16 +1363,16 @@
         <v>2001</v>
       </c>
       <c r="B26">
-        <v>418966.6093517293</v>
+        <v>418966.6234521187</v>
       </c>
       <c r="C26">
-        <v>190726.8930573034</v>
+        <v>190726.8943128761</v>
       </c>
       <c r="D26">
-        <v>345622.8450385159</v>
+        <v>345618.3149605152</v>
       </c>
       <c r="E26">
-        <v>163111.1221607288</v>
+        <v>163109.3368610477</v>
       </c>
     </row>
     <row r="27">
@@ -1380,16 +1380,16 @@
         <v>2002</v>
       </c>
       <c r="B27">
-        <v>408204.0356466301</v>
+        <v>408204.0520448756</v>
       </c>
       <c r="C27">
-        <v>175667.8276107399</v>
+        <v>175667.8344836868</v>
       </c>
       <c r="D27">
-        <v>337974.4977977844</v>
+        <v>337970.2120904999</v>
       </c>
       <c r="E27">
-        <v>151459.0764316793</v>
+        <v>151457.518002851</v>
       </c>
     </row>
     <row r="28">
@@ -1397,16 +1397,16 @@
         <v>2003</v>
       </c>
       <c r="B28">
-        <v>385559.3589082839</v>
+        <v>385559.3724923821</v>
       </c>
       <c r="C28">
-        <v>164759.8982664042</v>
+        <v>164759.906594749</v>
       </c>
       <c r="D28">
-        <v>322835.7052230555</v>
+        <v>322831.8203327322</v>
       </c>
       <c r="E28">
-        <v>142404.7419752087</v>
+        <v>142403.2984699018</v>
       </c>
     </row>
     <row r="29">
@@ -1414,16 +1414,16 @@
         <v>2004</v>
       </c>
       <c r="B29">
-        <v>352731.4677292184</v>
+        <v>352731.4771003778</v>
       </c>
       <c r="C29">
-        <v>163927.3522982867</v>
+        <v>163927.3563569855</v>
       </c>
       <c r="D29">
-        <v>300095.6042386473</v>
+        <v>300092.2725143235</v>
       </c>
       <c r="E29">
-        <v>142601.5815154462</v>
+        <v>142600.2002623676</v>
       </c>
     </row>
     <row r="30">
@@ -1431,16 +1431,16 @@
         <v>2005</v>
       </c>
       <c r="B30">
-        <v>309958.2747489224</v>
+        <v>309958.2839424828</v>
       </c>
       <c r="C30">
-        <v>152629.0706470647</v>
+        <v>152629.0716771489</v>
       </c>
       <c r="D30">
-        <v>267986.4329108098</v>
+        <v>267983.6452090585</v>
       </c>
       <c r="E30">
-        <v>134040.0943093481</v>
+        <v>134038.8786672072</v>
       </c>
     </row>
     <row r="31">
@@ -1448,16 +1448,16 @@
         <v>2006</v>
       </c>
       <c r="B31">
-        <v>286199.1805511705</v>
+        <v>286199.1920723048</v>
       </c>
       <c r="C31">
-        <v>134372.1059051807</v>
+        <v>134372.1085380388</v>
       </c>
       <c r="D31">
-        <v>250898.7745554525</v>
+        <v>250896.2983301547</v>
       </c>
       <c r="E31">
-        <v>120041.4366900213</v>
+        <v>120040.4814328143</v>
       </c>
     </row>
     <row r="32">
@@ -1465,16 +1465,16 @@
         <v>2007</v>
       </c>
       <c r="B32">
-        <v>292935.7710625533</v>
+        <v>292935.7829723977</v>
       </c>
       <c r="C32">
-        <v>110931.4665719992</v>
+        <v>110931.4713342069</v>
       </c>
       <c r="D32">
-        <v>256036.9581628628</v>
+        <v>256034.3489928366</v>
       </c>
       <c r="E32">
-        <v>100423.5713511817</v>
+        <v>100422.8634748468</v>
       </c>
     </row>
     <row r="33">
@@ -1482,16 +1482,16 @@
         <v>2008</v>
       </c>
       <c r="B33">
-        <v>329768.3182689333</v>
+        <v>329768.3292356476</v>
       </c>
       <c r="C33">
-        <v>91410.09111505041</v>
+        <v>91410.09477526846</v>
       </c>
       <c r="D33">
-        <v>282459.5302022885</v>
+        <v>282456.4610806239</v>
       </c>
       <c r="E33">
-        <v>82739.61951062482</v>
+        <v>82739.04913130596</v>
       </c>
     </row>
     <row r="34">
@@ -1499,16 +1499,16 @@
         <v>2009</v>
       </c>
       <c r="B34">
-        <v>374438.0260828004</v>
+        <v>374438.0365729519</v>
       </c>
       <c r="C34">
-        <v>90367.86751282823</v>
+        <v>90367.86806575903</v>
       </c>
       <c r="D34">
-        <v>318668.7044799238</v>
+        <v>318665.1932977583</v>
       </c>
       <c r="E34">
-        <v>80245.9318493852</v>
+        <v>80245.29926478156</v>
       </c>
     </row>
     <row r="35">
@@ -1516,16 +1516,16 @@
         <v>2010</v>
       </c>
       <c r="B35">
-        <v>418452.4855578237</v>
+        <v>418452.5004066911</v>
       </c>
       <c r="C35">
-        <v>121541.2664318572</v>
+        <v>121541.2688044056</v>
       </c>
       <c r="D35">
-        <v>357910.8060799528</v>
+        <v>357907.1042009583</v>
       </c>
       <c r="E35">
-        <v>107801.4218960013</v>
+        <v>107800.5784328368</v>
       </c>
     </row>
     <row r="36">
@@ -1533,16 +1533,16 @@
         <v>2011</v>
       </c>
       <c r="B36">
-        <v>409256.949045294</v>
+        <v>409256.964034889</v>
       </c>
       <c r="C36">
-        <v>140223.9889949395</v>
+        <v>140223.9919598005</v>
       </c>
       <c r="D36">
-        <v>351573.2385411518</v>
+        <v>351569.731279894</v>
       </c>
       <c r="E36">
-        <v>124297.8154304306</v>
+        <v>124296.8269924686</v>
       </c>
     </row>
     <row r="37">
@@ -1550,16 +1550,16 @@
         <v>2012</v>
       </c>
       <c r="B37">
-        <v>374341.7288949807</v>
+        <v>374341.744817575</v>
       </c>
       <c r="C37">
-        <v>143302.7476554025</v>
+        <v>143302.7501035137</v>
       </c>
       <c r="D37">
-        <v>322924.499549792</v>
+        <v>322921.3421398885</v>
       </c>
       <c r="E37">
-        <v>126635.5352957309</v>
+        <v>126634.4982850318</v>
       </c>
     </row>
     <row r="38">
@@ -1567,16 +1567,16 @@
         <v>2013</v>
       </c>
       <c r="B38">
-        <v>348171.3504759462</v>
+        <v>348171.3656212806</v>
       </c>
       <c r="C38">
-        <v>137754.0567987314</v>
+        <v>137754.060672575</v>
       </c>
       <c r="D38">
-        <v>299330.6954190073</v>
+        <v>299327.7111048182</v>
       </c>
       <c r="E38">
-        <v>122575.6064600861</v>
+        <v>122574.6505299416</v>
       </c>
     </row>
     <row r="39">
@@ -1584,16 +1584,16 @@
         <v>2014</v>
       </c>
       <c r="B39">
-        <v>338218.3771407067</v>
+        <v>338218.3896191957</v>
       </c>
       <c r="C39">
-        <v>120972.6259369012</v>
+        <v>120972.6311053807</v>
       </c>
       <c r="D39">
-        <v>286725.8010744424</v>
+        <v>286722.798319069</v>
       </c>
       <c r="E39">
-        <v>108533.2459143826</v>
+        <v>108532.4601771811</v>
       </c>
     </row>
     <row r="40">
@@ -1601,16 +1601,16 @@
         <v>2015</v>
       </c>
       <c r="B40">
-        <v>303073.3517752681</v>
+        <v>303073.3610568399</v>
       </c>
       <c r="C40">
-        <v>96639.70510822169</v>
+        <v>96639.70821922124</v>
       </c>
       <c r="D40">
-        <v>251538.9119636215</v>
+        <v>251535.9559142754</v>
       </c>
       <c r="E40">
-        <v>84869.90595002697</v>
+        <v>84869.17249923584</v>
       </c>
     </row>
     <row r="41">
@@ -1618,16 +1618,16 @@
         <v>2016</v>
       </c>
       <c r="B41">
-        <v>254962.3757241565</v>
+        <v>254962.3842037397</v>
       </c>
       <c r="C41">
-        <v>92951.68169067478</v>
+        <v>92951.68242668931</v>
       </c>
       <c r="D41">
-        <v>207763.8645108429</v>
+        <v>207761.141450995</v>
       </c>
       <c r="E41">
-        <v>78472.86471783508</v>
+        <v>78471.99670319974</v>
       </c>
     </row>
     <row r="42">
@@ -1635,16 +1635,16 @@
         <v>2017</v>
       </c>
       <c r="B42">
-        <v>206241.9847931759</v>
+        <v>206241.9919652617</v>
       </c>
       <c r="C42">
-        <v>93539.54110799408</v>
+        <v>93539.54266159181</v>
       </c>
       <c r="D42">
-        <v>164343.1876874236</v>
+        <v>164340.6924829663</v>
       </c>
       <c r="E42">
-        <v>76264.65605234362</v>
+        <v>76263.62365554855</v>
       </c>
     </row>
     <row r="43">
@@ -1652,16 +1652,16 @@
         <v>2018</v>
       </c>
       <c r="B43">
-        <v>174413.8700493125</v>
+        <v>174413.8752691078</v>
       </c>
       <c r="C43">
-        <v>80091.84255675947</v>
+        <v>80091.84616234903</v>
       </c>
       <c r="D43">
-        <v>134020.6551118644</v>
+        <v>134018.1713197495</v>
       </c>
       <c r="E43">
-        <v>62622.66888577645</v>
+        <v>62621.59002320784</v>
       </c>
     </row>
     <row r="44">
@@ -1669,16 +1669,16 @@
         <v>2019</v>
       </c>
       <c r="B44">
-        <v>186964.3647670322</v>
+        <v>186964.3687577888</v>
       </c>
       <c r="C44">
-        <v>77994.6555068044</v>
+        <v>77994.65849710979</v>
       </c>
       <c r="D44">
-        <v>145031.2708453953</v>
+        <v>145028.6542861808</v>
       </c>
       <c r="E44">
-        <v>62335.99020516699</v>
+        <v>62334.97572368169</v>
       </c>
     </row>
     <row r="45">
@@ -1686,16 +1686,16 @@
         <v>2020</v>
       </c>
       <c r="B45">
-        <v>202582.0651684772</v>
+        <v>202582.0699674013</v>
       </c>
       <c r="C45">
-        <v>76644.99762629192</v>
+        <v>76644.99837004802</v>
       </c>
       <c r="D45">
-        <v>158514.9017511738</v>
+        <v>158512.1681653596</v>
       </c>
       <c r="E45">
-        <v>62084.11870894234</v>
+        <v>62083.14389359258</v>
       </c>
     </row>
     <row r="46">
@@ -1703,16 +1703,16 @@
         <v>2021</v>
       </c>
       <c r="B46">
-        <v>223889.4712543478</v>
+        <v>223889.4776623909</v>
       </c>
       <c r="C46">
-        <v>91001.96215928708</v>
+        <v>91001.96258823808</v>
       </c>
       <c r="D46">
-        <v>180976.7492451337</v>
+        <v>180974.0245377118</v>
       </c>
       <c r="E46">
-        <v>76232.17260467316</v>
+        <v>76231.16771312035</v>
       </c>
     </row>
     <row r="47">
@@ -1720,16 +1720,16 @@
         <v>2022</v>
       </c>
       <c r="B47">
-        <v>233395.3344446474</v>
+        <v>233395.3401302278</v>
       </c>
       <c r="C47">
-        <v>100896.1723192542</v>
+        <v>100896.1748708622</v>
       </c>
       <c r="D47">
-        <v>192628.6979403109</v>
+        <v>192626.0138058314</v>
       </c>
       <c r="E47">
-        <v>86037.15383534474</v>
+        <v>86036.12054651986</v>
       </c>
     </row>
     <row r="48">
@@ -1737,16 +1737,16 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>238585.2948933406</v>
+        <v>238585.2984186699</v>
       </c>
       <c r="C48">
-        <v>100395.4239482632</v>
+        <v>100395.4279455645</v>
       </c>
       <c r="D48">
-        <v>198466.3742309352</v>
+        <v>198463.7089091204</v>
       </c>
       <c r="E48">
-        <v>86885.01085074962</v>
+        <v>86884.04314936523</v>
       </c>
     </row>
     <row r="49">
@@ -1754,16 +1754,16 @@
         <v>2024</v>
       </c>
       <c r="B49">
-        <v>250885.6246673522</v>
+        <v>250885.6261193536</v>
       </c>
       <c r="C49">
-        <v>100901.0198987257</v>
+        <v>100901.0219219392</v>
       </c>
       <c r="D49">
-        <v>210213.5934781413</v>
+        <v>210210.8803300725</v>
       </c>
       <c r="E49">
-        <v>88984.68699307635</v>
+        <v>88983.81083721059</v>
       </c>
     </row>
     <row r="50">
@@ -1771,16 +1771,16 @@
         <v>2025</v>
       </c>
       <c r="B50">
-        <v>264554.6262630097</v>
+        <v>264554.6276249213</v>
       </c>
       <c r="C50">
-        <v>104071.727732353</v>
+        <v>104071.7271925989</v>
       </c>
       <c r="D50">
-        <v>219458.564627805</v>
+        <v>219455.6515061877</v>
       </c>
       <c r="E50">
-        <v>93152.4678520602</v>
+        <v>93151.63439255896</v>
       </c>
     </row>
   </sheetData>
@@ -1810,7 +1810,7 @@
         <v>1977</v>
       </c>
       <c r="B2">
-        <v>958.9809387131442</v>
+        <v>958.9687544141135</v>
       </c>
     </row>
     <row r="3">
@@ -1818,7 +1818,7 @@
         <v>1978</v>
       </c>
       <c r="B3">
-        <v>2692.008468896808</v>
+        <v>2691.961019692406</v>
       </c>
     </row>
     <row r="4">
@@ -1826,7 +1826,7 @@
         <v>1979</v>
       </c>
       <c r="B4">
-        <v>2207.773557660196</v>
+        <v>2207.73947917075</v>
       </c>
     </row>
     <row r="5">
@@ -1834,7 +1834,7 @@
         <v>1980</v>
       </c>
       <c r="B5">
-        <v>1798.104349813064</v>
+        <v>1798.066520815665</v>
       </c>
     </row>
     <row r="6">
@@ -1842,7 +1842,7 @@
         <v>1981</v>
       </c>
       <c r="B6">
-        <v>2906.994732224369</v>
+        <v>2906.925603148202</v>
       </c>
     </row>
     <row r="7">
@@ -1850,7 +1850,7 @@
         <v>1982</v>
       </c>
       <c r="B7">
-        <v>2917.613521978754</v>
+        <v>2917.544978310828</v>
       </c>
     </row>
     <row r="8">
@@ -1858,7 +1858,7 @@
         <v>1983</v>
       </c>
       <c r="B8">
-        <v>3115.705273616662</v>
+        <v>3115.638293880506</v>
       </c>
     </row>
     <row r="9">
@@ -1866,7 +1866,7 @@
         <v>1984</v>
       </c>
       <c r="B9">
-        <v>2787.830656557526</v>
+        <v>2787.777100593783</v>
       </c>
     </row>
     <row r="10">
@@ -1874,7 +1874,7 @@
         <v>1985</v>
       </c>
       <c r="B10">
-        <v>3678.555849766847</v>
+        <v>3678.49498915656</v>
       </c>
     </row>
     <row r="11">
@@ -1882,7 +1882,7 @@
         <v>1986</v>
       </c>
       <c r="B11">
-        <v>4445.426065610618</v>
+        <v>4445.364416629639</v>
       </c>
     </row>
     <row r="12">
@@ -1890,7 +1890,7 @@
         <v>1987</v>
       </c>
       <c r="B12">
-        <v>3929.088041717308</v>
+        <v>3929.042228723316</v>
       </c>
     </row>
     <row r="13">
@@ -1898,7 +1898,7 @@
         <v>1988</v>
       </c>
       <c r="B13">
-        <v>3866.880535684072</v>
+        <v>3866.83466782426</v>
       </c>
     </row>
     <row r="14">
@@ -1906,7 +1906,7 @@
         <v>1989</v>
       </c>
       <c r="B14">
-        <v>3747.053889464983</v>
+        <v>3747.007338246302</v>
       </c>
     </row>
     <row r="15">
@@ -1914,7 +1914,7 @@
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>4363.351021004918</v>
+        <v>4363.294242110647</v>
       </c>
     </row>
     <row r="16">
@@ -1922,7 +1922,7 @@
         <v>1991</v>
       </c>
       <c r="B16">
-        <v>5813.88708536718</v>
+        <v>5813.816384109096</v>
       </c>
     </row>
     <row r="17">
@@ -1930,7 +1930,7 @@
         <v>1992</v>
       </c>
       <c r="B17">
-        <v>5907.499846995659</v>
+        <v>5907.443986823646</v>
       </c>
     </row>
     <row r="18">
@@ -1938,7 +1938,7 @@
         <v>1993</v>
       </c>
       <c r="B18">
-        <v>5472.103488800649</v>
+        <v>5472.069622675082</v>
       </c>
     </row>
     <row r="19">
@@ -1946,7 +1946,7 @@
         <v>1994</v>
       </c>
       <c r="B19">
-        <v>5095.299881890866</v>
+        <v>5095.277714796276</v>
       </c>
     </row>
     <row r="20">
@@ -1954,7 +1954,7 @@
         <v>1995</v>
       </c>
       <c r="B20">
-        <v>4627.516338607572</v>
+        <v>4627.505706520315</v>
       </c>
     </row>
     <row r="21">
@@ -1962,7 +1962,7 @@
         <v>1996</v>
       </c>
       <c r="B21">
-        <v>5605.345299212286</v>
+        <v>5605.336130228024</v>
       </c>
     </row>
     <row r="22">
@@ -1970,7 +1970,7 @@
         <v>1997</v>
       </c>
       <c r="B22">
-        <v>4799.230227677914</v>
+        <v>4799.223866895441</v>
       </c>
     </row>
     <row r="23">
@@ -1978,7 +1978,7 @@
         <v>1998</v>
       </c>
       <c r="B23">
-        <v>3954.951404471075</v>
+        <v>3954.948586807308</v>
       </c>
     </row>
     <row r="24">
@@ -1986,7 +1986,7 @@
         <v>1999</v>
       </c>
       <c r="B24">
-        <v>2772.938551846311</v>
+        <v>2772.934427436239</v>
       </c>
     </row>
     <row r="25">
@@ -1994,7 +1994,7 @@
         <v>2000</v>
       </c>
       <c r="B25">
-        <v>3192.068849973965</v>
+        <v>3192.061414604505</v>
       </c>
     </row>
     <row r="26">
@@ -2002,7 +2002,7 @@
         <v>2001</v>
       </c>
       <c r="B26">
-        <v>3517.50774415598</v>
+        <v>3517.502112791858</v>
       </c>
     </row>
     <row r="27">
@@ -2010,7 +2010,7 @@
         <v>2002</v>
       </c>
       <c r="B27">
-        <v>2816.089841501365</v>
+        <v>2816.087589576238</v>
       </c>
     </row>
     <row r="28">
@@ -2018,7 +2018,7 @@
         <v>2003</v>
       </c>
       <c r="B28">
-        <v>3050.372326250301</v>
+        <v>3050.3743664637</v>
       </c>
     </row>
     <row r="29">
@@ -2026,7 +2026,7 @@
         <v>2004</v>
       </c>
       <c r="B29">
-        <v>3097.616703150332</v>
+        <v>3097.621420252041</v>
       </c>
     </row>
     <row r="30">
@@ -2034,7 +2034,7 @@
         <v>2005</v>
       </c>
       <c r="B30">
-        <v>3912.890088910251</v>
+        <v>3912.894756358517</v>
       </c>
     </row>
     <row r="31">
@@ -2042,7 +2042,7 @@
         <v>2006</v>
       </c>
       <c r="B31">
-        <v>5041.24811961665</v>
+        <v>5041.250718945676</v>
       </c>
     </row>
     <row r="32">
@@ -2050,7 +2050,7 @@
         <v>2007</v>
       </c>
       <c r="B32">
-        <v>6323.247541532055</v>
+        <v>6323.252927812684</v>
       </c>
     </row>
     <row r="33">
@@ -2058,7 +2058,7 @@
         <v>2008</v>
       </c>
       <c r="B33">
-        <v>5339.11332876405</v>
+        <v>5339.118866178153</v>
       </c>
     </row>
     <row r="34">
@@ -2066,7 +2066,7 @@
         <v>2009</v>
       </c>
       <c r="B34">
-        <v>5052.740852506824</v>
+        <v>5052.747742376025</v>
       </c>
     </row>
     <row r="35">
@@ -2074,7 +2074,7 @@
         <v>2010</v>
       </c>
       <c r="B35">
-        <v>3882.626556741612</v>
+        <v>3882.633017132572</v>
       </c>
     </row>
     <row r="36">
@@ -2082,7 +2082,7 @@
         <v>2011</v>
       </c>
       <c r="B36">
-        <v>2848.867213419113</v>
+        <v>2848.869174927039</v>
       </c>
     </row>
     <row r="37">
@@ -2090,7 +2090,7 @@
         <v>2012</v>
       </c>
       <c r="B37">
-        <v>2713.622858749542</v>
+        <v>2713.62164009188</v>
       </c>
     </row>
     <row r="38">
@@ -2098,7 +2098,7 @@
         <v>2013</v>
       </c>
       <c r="B38">
-        <v>2639.510143039549</v>
+        <v>2639.506234386302</v>
       </c>
     </row>
     <row r="39">
@@ -2106,7 +2106,7 @@
         <v>2014</v>
       </c>
       <c r="B39">
-        <v>1497.599919255548</v>
+        <v>1497.594158612404</v>
       </c>
     </row>
     <row r="40">
@@ -2114,7 +2114,7 @@
         <v>2015</v>
       </c>
       <c r="B40">
-        <v>961.3718947408059</v>
+        <v>961.3643020470674</v>
       </c>
     </row>
     <row r="41">
@@ -2122,7 +2122,7 @@
         <v>2016</v>
       </c>
       <c r="B41">
-        <v>733.1464287253342</v>
+        <v>733.1398658599021</v>
       </c>
     </row>
     <row r="42">
@@ -2130,7 +2130,7 @@
         <v>2017</v>
       </c>
       <c r="B42">
-        <v>1080.685049779295</v>
+        <v>1080.676511275825</v>
       </c>
     </row>
     <row r="43">
@@ -2138,7 +2138,7 @@
         <v>2018</v>
       </c>
       <c r="B43">
-        <v>1476.145589222232</v>
+        <v>1476.136391274179</v>
       </c>
     </row>
     <row r="44">
@@ -2146,7 +2146,7 @@
         <v>2019</v>
       </c>
       <c r="B44">
-        <v>1656.81174138616</v>
+        <v>1656.803393832253</v>
       </c>
     </row>
     <row r="45">
@@ -2154,7 +2154,7 @@
         <v>2020</v>
       </c>
       <c r="B45">
-        <v>1176.582119770435</v>
+        <v>1176.577863732073</v>
       </c>
     </row>
     <row r="46">
@@ -2162,7 +2162,7 @@
         <v>2021</v>
       </c>
       <c r="B46">
-        <v>1376.23024395588</v>
+        <v>1376.22619531371</v>
       </c>
     </row>
     <row r="47">
@@ -2170,7 +2170,7 @@
         <v>2022</v>
       </c>
       <c r="B47">
-        <v>2058.43610054928</v>
+        <v>2058.431907494391</v>
       </c>
     </row>
     <row r="48">
@@ -2178,7 +2178,7 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>1904.090562976898</v>
+        <v>1904.086454399429</v>
       </c>
     </row>
     <row r="49">
@@ -2186,7 +2186,7 @@
         <v>2024</v>
       </c>
       <c r="B49">
-        <v>2059.54419017966</v>
+        <v>2059.531184796147</v>
       </c>
     </row>
     <row r="50">
@@ -2194,7 +2194,7 @@
         <v>2025</v>
       </c>
       <c r="B50">
-        <v>2220.490806547664</v>
+        <v>2220.472208980446</v>
       </c>
     </row>
   </sheetData>
@@ -2229,10 +2229,10 @@
         <v>1977</v>
       </c>
       <c r="B2">
-        <v>449329.9295218305</v>
+        <v>104134.5525149916</v>
       </c>
       <c r="C2">
-        <v>488243.7564804981</v>
+        <v>156307.3725890305</v>
       </c>
     </row>
     <row r="3">
@@ -2240,10 +2240,10 @@
         <v>1978</v>
       </c>
       <c r="B3">
-        <v>537958.8575245664</v>
+        <v>122739.1710480768</v>
       </c>
       <c r="C3">
-        <v>566874.6969966071</v>
+        <v>192283.8665324071</v>
       </c>
     </row>
     <row r="4">
@@ -2251,10 +2251,10 @@
         <v>1979</v>
       </c>
       <c r="B4">
-        <v>541756.4430342679</v>
+        <v>113273.928729621</v>
       </c>
       <c r="C4">
-        <v>613822.4795181077</v>
+        <v>250309.5452246538</v>
       </c>
     </row>
     <row r="5">
@@ -2262,10 +2262,10 @@
         <v>1980</v>
       </c>
       <c r="B5">
-        <v>555806.0109270304</v>
+        <v>111940.6216387978</v>
       </c>
       <c r="C5">
-        <v>714438.1250201357</v>
+        <v>305073.8027009263</v>
       </c>
     </row>
     <row r="6">
@@ -2273,10 +2273,10 @@
         <v>1981</v>
       </c>
       <c r="B6">
-        <v>756451.0252921799</v>
+        <v>237400.0345085331</v>
       </c>
       <c r="C6">
-        <v>848203.3570142448</v>
+        <v>388259.108029335</v>
       </c>
     </row>
     <row r="7">
@@ -2284,10 +2284,10 @@
         <v>1982</v>
       </c>
       <c r="B7">
-        <v>765366.9787305348</v>
+        <v>218729.5824694092</v>
       </c>
       <c r="C7">
-        <v>872968.3327487061</v>
+        <v>391343.135076751</v>
       </c>
     </row>
     <row r="8">
@@ -2295,10 +2295,10 @@
         <v>1983</v>
       </c>
       <c r="B8">
-        <v>1048015.231775717</v>
+        <v>276465.7776824433</v>
       </c>
       <c r="C8">
-        <v>1211432.438296361</v>
+        <v>504358.1296089365</v>
       </c>
     </row>
     <row r="9">
@@ -2306,10 +2306,10 @@
         <v>1984</v>
       </c>
       <c r="B9">
-        <v>1258089.01901066</v>
+        <v>352833.8441962747</v>
       </c>
       <c r="C9">
-        <v>1406214.325804202</v>
+        <v>554588.9066754566</v>
       </c>
     </row>
     <row r="10">
@@ -2317,10 +2317,10 @@
         <v>1985</v>
       </c>
       <c r="B10">
-        <v>1585373.887215224</v>
+        <v>433484.2758251461</v>
       </c>
       <c r="C10">
-        <v>1710243.349430549</v>
+        <v>622063.7466701154</v>
       </c>
     </row>
     <row r="11">
@@ -2328,10 +2328,10 @@
         <v>1986</v>
       </c>
       <c r="B11">
-        <v>1989668.224242259</v>
+        <v>487291.4829182797</v>
       </c>
       <c r="C11">
-        <v>2125541.250793064</v>
+        <v>713986.4344509016</v>
       </c>
     </row>
     <row r="12">
@@ -2339,10 +2339,10 @@
         <v>1987</v>
       </c>
       <c r="B12">
-        <v>2410007.100427695</v>
+        <v>529220.57065344</v>
       </c>
       <c r="C12">
-        <v>2620859.538088952</v>
+        <v>824367.5834833947</v>
       </c>
     </row>
     <row r="13">
@@ -2350,10 +2350,10 @@
         <v>1988</v>
       </c>
       <c r="B13">
-        <v>2534523.7676791</v>
+        <v>576590.220831506</v>
       </c>
       <c r="C13">
-        <v>2728975.031699232</v>
+        <v>834293.6707840753</v>
       </c>
     </row>
     <row r="14">
@@ -2361,10 +2361,10 @@
         <v>1989</v>
       </c>
       <c r="B14">
-        <v>2685778.849280925</v>
+        <v>612479.3013568564</v>
       </c>
       <c r="C14">
-        <v>2820595.080949347</v>
+        <v>815017.9218289607</v>
       </c>
     </row>
     <row r="15">
@@ -2372,10 +2372,10 @@
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>2856655.576685118</v>
+        <v>589165.5757666521</v>
       </c>
       <c r="C15">
-        <v>3016105.38534133</v>
+        <v>807906.8043009307</v>
       </c>
     </row>
     <row r="16">
@@ -2383,10 +2383,10 @@
         <v>1991</v>
       </c>
       <c r="B16">
-        <v>2885415.001292569</v>
+        <v>589142.6886263913</v>
       </c>
       <c r="C16">
-        <v>3023804.54935436</v>
+        <v>800658.6099843748</v>
       </c>
     </row>
     <row r="17">
@@ -2394,10 +2394,10 @@
         <v>1992</v>
       </c>
       <c r="B17">
-        <v>2839410.1216769</v>
+        <v>563116.8893854044</v>
       </c>
       <c r="C17">
-        <v>3005741.452831681</v>
+        <v>804897.6934037891</v>
       </c>
     </row>
     <row r="18">
@@ -2405,10 +2405,10 @@
         <v>1993</v>
       </c>
       <c r="B18">
-        <v>2549749.507666031</v>
+        <v>529552.9425449015</v>
       </c>
       <c r="C18">
-        <v>2721887.044633934</v>
+        <v>754186.335881222</v>
       </c>
     </row>
     <row r="19">
@@ -2416,10 +2416,10 @@
         <v>1994</v>
       </c>
       <c r="B19">
-        <v>2604832.302676712</v>
+        <v>565523.098127569</v>
       </c>
       <c r="C19">
-        <v>2726662.963591389</v>
+        <v>735406.6033886751</v>
       </c>
     </row>
     <row r="20">
@@ -2427,10 +2427,10 @@
         <v>1995</v>
       </c>
       <c r="B20">
-        <v>2539167.569587063</v>
+        <v>514278.8820558098</v>
       </c>
       <c r="C20">
-        <v>2644964.081378874</v>
+        <v>663668.7935554113</v>
       </c>
     </row>
     <row r="21">
@@ -2438,10 +2438,10 @@
         <v>1996</v>
       </c>
       <c r="B21">
-        <v>2458676.188742215</v>
+        <v>481571.6716257796</v>
       </c>
       <c r="C21">
-        <v>2559193.029940736</v>
+        <v>635930.4856650754</v>
       </c>
     </row>
     <row r="22">
@@ -2449,10 +2449,10 @@
         <v>1997</v>
       </c>
       <c r="B22">
-        <v>2238281.273502134</v>
+        <v>414808.5060431225</v>
       </c>
       <c r="C22">
-        <v>2354344.312160063</v>
+        <v>583646.8550427158</v>
       </c>
     </row>
     <row r="23">
@@ -2460,10 +2460,10 @@
         <v>1998</v>
       </c>
       <c r="B23">
-        <v>2143194.172531458</v>
+        <v>407875.4985741221</v>
       </c>
       <c r="C23">
-        <v>2280486.676888221</v>
+        <v>588380.7835311928</v>
       </c>
     </row>
     <row r="24">
@@ -2471,10 +2471,10 @@
         <v>1999</v>
       </c>
       <c r="B24">
-        <v>1705829.177957692</v>
+        <v>340086.9303868429</v>
       </c>
       <c r="C24">
-        <v>1797582.016542162</v>
+        <v>466599.3079156019</v>
       </c>
     </row>
     <row r="25">
@@ -2482,10 +2482,10 @@
         <v>2000</v>
       </c>
       <c r="B25">
-        <v>1452785.71197879</v>
+        <v>299133.77454786</v>
       </c>
       <c r="C25">
-        <v>1535216.706567807</v>
+        <v>420720.9766128066</v>
       </c>
     </row>
     <row r="26">
@@ -2493,10 +2493,10 @@
         <v>2001</v>
       </c>
       <c r="B26">
-        <v>1321011.023746911</v>
+        <v>279625.4263889897</v>
       </c>
       <c r="C26">
-        <v>1409758.763530657</v>
+        <v>417620.7314096555</v>
       </c>
     </row>
     <row r="27">
@@ -2504,10 +2504,10 @@
         <v>2002</v>
       </c>
       <c r="B27">
-        <v>1133386.015900963</v>
+        <v>236957.3937948454</v>
       </c>
       <c r="C27">
-        <v>1236754.915531229</v>
+        <v>376766.4332998166</v>
       </c>
     </row>
     <row r="28">
@@ -2515,10 +2515,10 @@
         <v>2003</v>
       </c>
       <c r="B28">
-        <v>1190137.906694702</v>
+        <v>270993.5218235647</v>
       </c>
       <c r="C28">
-        <v>1289159.488328038</v>
+        <v>397551.4181783332</v>
       </c>
     </row>
     <row r="29">
@@ -2526,10 +2526,10 @@
         <v>2004</v>
       </c>
       <c r="B29">
-        <v>1102394.610093884</v>
+        <v>254882.9247013658</v>
       </c>
       <c r="C29">
-        <v>1163666.614806109</v>
+        <v>340958.724643992</v>
       </c>
     </row>
     <row r="30">
@@ -2537,10 +2537,10 @@
         <v>2005</v>
       </c>
       <c r="B30">
-        <v>1042085.599480947</v>
+        <v>228424.5716707645</v>
       </c>
       <c r="C30">
-        <v>1099248.282723703</v>
+        <v>313816.4093819049</v>
       </c>
     </row>
     <row r="31">
@@ -2548,10 +2548,10 @@
         <v>2006</v>
       </c>
       <c r="B31">
-        <v>919015.7015772122</v>
+        <v>187991.3593872076</v>
       </c>
       <c r="C31">
-        <v>976602.8215443341</v>
+        <v>286558.3265620955</v>
       </c>
     </row>
     <row r="32">
@@ -2559,10 +2559,10 @@
         <v>2007</v>
       </c>
       <c r="B32">
-        <v>743885.7462887937</v>
+        <v>145260.7607073284</v>
       </c>
       <c r="C32">
-        <v>821269.9729226971</v>
+        <v>283202.9243566759</v>
       </c>
     </row>
     <row r="33">
@@ -2570,10 +2570,10 @@
         <v>2008</v>
       </c>
       <c r="B33">
-        <v>623945.272538239</v>
+        <v>129724.1837780683</v>
       </c>
       <c r="C33">
-        <v>750908.8157430073</v>
+        <v>321589.1809949231</v>
       </c>
     </row>
     <row r="34">
@@ -2581,10 +2581,10 @@
         <v>2009</v>
       </c>
       <c r="B34">
-        <v>564769.9638020429</v>
+        <v>156131.7452650518</v>
       </c>
       <c r="C34">
-        <v>710359.5577671862</v>
+        <v>351084.724514499</v>
       </c>
     </row>
     <row r="35">
@@ -2592,10 +2592,10 @@
         <v>2010</v>
       </c>
       <c r="B35">
-        <v>863741.6780510624</v>
+        <v>253642.4394875036</v>
       </c>
       <c r="C35">
-        <v>993090.3223101934</v>
+        <v>438458.7821362952</v>
       </c>
     </row>
     <row r="36">
@@ -2603,10 +2603,10 @@
         <v>2011</v>
       </c>
       <c r="B36">
-        <v>874970.8360076441</v>
+        <v>232457.7449047212</v>
       </c>
       <c r="C36">
-        <v>1006177.538851652</v>
+        <v>392751.2615663867</v>
       </c>
     </row>
     <row r="37">
@@ -2614,10 +2614,10 @@
         <v>2012</v>
       </c>
       <c r="B37">
-        <v>877102.4052241937</v>
+        <v>240034.8654866435</v>
       </c>
       <c r="C37">
-        <v>944979.9366895964</v>
+        <v>344603.5757334184</v>
       </c>
     </row>
     <row r="38">
@@ -2625,10 +2625,10 @@
         <v>2013</v>
       </c>
       <c r="B38">
-        <v>826867.8083315933</v>
+        <v>199206.1377414824</v>
       </c>
       <c r="C38">
-        <v>909787.9803753739</v>
+        <v>326349.7135654368</v>
       </c>
     </row>
     <row r="39">
@@ -2636,10 +2636,10 @@
         <v>2014</v>
       </c>
       <c r="B39">
-        <v>794892.2331433366</v>
+        <v>169489.1207514885</v>
       </c>
       <c r="C39">
-        <v>898469.2392366759</v>
+        <v>314297.0211106346</v>
       </c>
     </row>
     <row r="40">
@@ -2647,10 +2647,10 @@
         <v>2015</v>
       </c>
       <c r="B40">
-        <v>706134.2600680802</v>
+        <v>166458.1080827868</v>
       </c>
       <c r="C40">
-        <v>825015.6499344951</v>
+        <v>302282.6784972339</v>
       </c>
     </row>
     <row r="41">
@@ -2658,10 +2658,10 @@
         <v>2016</v>
       </c>
       <c r="B41">
-        <v>655332.5450165451</v>
+        <v>183112.9513727978</v>
       </c>
       <c r="C41">
-        <v>709044.0569009725</v>
+        <v>247233.5717936106</v>
       </c>
     </row>
     <row r="42">
@@ -2669,10 +2669,10 @@
         <v>2017</v>
       </c>
       <c r="B42">
-        <v>546165.7274532005</v>
+        <v>138852.9104041859</v>
       </c>
       <c r="C42">
-        <v>571470.1121851755</v>
+        <v>178820.8112943319</v>
       </c>
     </row>
     <row r="43">
@@ -2680,10 +2680,10 @@
         <v>2018</v>
       </c>
       <c r="B43">
-        <v>457051.914289301</v>
+        <v>113723.6955286334</v>
       </c>
       <c r="C43">
-        <v>488779.1294880882</v>
+        <v>169197.3665577556</v>
       </c>
     </row>
     <row r="44">
@@ -2691,10 +2691,10 @@
         <v>2019</v>
       </c>
       <c r="B44">
-        <v>511249.0233325047</v>
+        <v>113579.3282096663</v>
       </c>
       <c r="C44">
-        <v>565668.7123414004</v>
+        <v>197362.665475976</v>
       </c>
     </row>
     <row r="45">
@@ -2702,10 +2702,10 @@
         <v>2020</v>
       </c>
       <c r="B45">
-        <v>465886.6759722386</v>
+        <v>114250.8996519885</v>
       </c>
       <c r="C45">
-        <v>522790.8264808835</v>
+        <v>192699.6596774861</v>
       </c>
     </row>
     <row r="46">
@@ -2713,10 +2713,10 @@
         <v>2021</v>
       </c>
       <c r="B46">
-        <v>578010.8732054279</v>
+        <v>139871.4393227159</v>
       </c>
       <c r="C46">
-        <v>630758.6689475775</v>
+        <v>211665.6997452844</v>
       </c>
     </row>
     <row r="47">
@@ -2724,10 +2724,10 @@
         <v>2022</v>
       </c>
       <c r="B47">
-        <v>702561.0224150716</v>
+        <v>164686.0853647432</v>
       </c>
       <c r="C47">
-        <v>746933.6927726311</v>
+        <v>239692.8754463358</v>
       </c>
     </row>
     <row r="48">
@@ -2735,10 +2735,10 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>648425.109178227</v>
+        <v>143767.18566002</v>
       </c>
       <c r="C48">
-        <v>711596.0869047955</v>
+        <v>234727.9001282548</v>
       </c>
     </row>
     <row r="49">
@@ -2746,10 +2746,10 @@
         <v>2024</v>
       </c>
       <c r="B49">
-        <v>696456.2120422517</v>
+        <v>160129.7041176843</v>
       </c>
       <c r="C49">
-        <v>762655.4487810951</v>
+        <v>253477.9186428221</v>
       </c>
     </row>
     <row r="50">
@@ -2757,10 +2757,10 @@
         <v>2025</v>
       </c>
       <c r="B50">
-        <v>728063.3508493296</v>
+        <v>170646.9782041942</v>
       </c>
       <c r="C50">
-        <v>788790.2595776399</v>
+        <v>262051.4215312043</v>
       </c>
     </row>
   </sheetData>

--- a/GOA CEATTLE/Model runs/GOA_25/Results/GOA 2025 Cod ESP Indices.xlsx
+++ b/GOA CEATTLE/Model runs/GOA_25/Results/GOA 2025 Cod ESP Indices.xlsx
@@ -379,7 +379,7 @@
         <v>1977</v>
       </c>
       <c r="B2">
-        <v>0.6284140835672848</v>
+        <v>0.6736426724522603</v>
       </c>
       <c r="C2">
         <v>0.492942</v>
@@ -390,7 +390,7 @@
         <v>1978</v>
       </c>
       <c r="B3">
-        <v>0.6055639886084474</v>
+        <v>0.6473587614426651</v>
       </c>
       <c r="C3">
         <v>0.492942</v>
@@ -401,7 +401,7 @@
         <v>1979</v>
       </c>
       <c r="B4">
-        <v>0.5810784784267289</v>
+        <v>0.6170726542617464</v>
       </c>
       <c r="C4">
         <v>0.492942</v>
@@ -412,7 +412,7 @@
         <v>1980</v>
       </c>
       <c r="B5">
-        <v>0.5801971771023227</v>
+        <v>0.6153349272980131</v>
       </c>
       <c r="C5">
         <v>0.492942</v>
@@ -423,7 +423,7 @@
         <v>1981</v>
       </c>
       <c r="B6">
-        <v>0.6094188651830434</v>
+        <v>0.6463683197417087</v>
       </c>
       <c r="C6">
         <v>0.492942</v>
@@ -434,7 +434,7 @@
         <v>1982</v>
       </c>
       <c r="B7">
-        <v>0.5958546103890016</v>
+        <v>0.6290548952497774</v>
       </c>
       <c r="C7">
         <v>0.492942</v>
@@ -445,7 +445,7 @@
         <v>1983</v>
       </c>
       <c r="B8">
-        <v>0.6270325007028805</v>
+        <v>0.6618639326722737</v>
       </c>
       <c r="C8">
         <v>0.492942</v>
@@ -456,7 +456,7 @@
         <v>1984</v>
       </c>
       <c r="B9">
-        <v>0.6267295912662285</v>
+        <v>0.6553999944477231</v>
       </c>
       <c r="C9">
         <v>0.492942</v>
@@ -467,7 +467,7 @@
         <v>1985</v>
       </c>
       <c r="B10">
-        <v>0.6178424903436113</v>
+        <v>0.6398436187170017</v>
       </c>
       <c r="C10">
         <v>0.492942</v>
@@ -478,7 +478,7 @@
         <v>1986</v>
       </c>
       <c r="B11">
-        <v>0.6174956352175619</v>
+        <v>0.6370515423519476</v>
       </c>
       <c r="C11">
         <v>0.492942</v>
@@ -489,7 +489,7 @@
         <v>1987</v>
       </c>
       <c r="B12">
-        <v>0.6267526773497661</v>
+        <v>0.6481494579448246</v>
       </c>
       <c r="C12">
         <v>0.492942</v>
@@ -500,7 +500,7 @@
         <v>1988</v>
       </c>
       <c r="B13">
-        <v>0.6241479675925681</v>
+        <v>0.6525429092403149</v>
       </c>
       <c r="C13">
         <v>0.492942</v>
@@ -511,7 +511,7 @@
         <v>1989</v>
       </c>
       <c r="B14">
-        <v>0.6491728290140465</v>
+        <v>0.6886303234721927</v>
       </c>
       <c r="C14">
         <v>0.492942</v>
@@ -522,7 +522,7 @@
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>0.6838355412701718</v>
+        <v>0.7293092404370561</v>
       </c>
       <c r="C15">
         <v>0.492942</v>
@@ -533,7 +533,7 @@
         <v>1991</v>
       </c>
       <c r="B16">
-        <v>0.7109006942161671</v>
+        <v>0.756341807348917</v>
       </c>
       <c r="C16">
         <v>0.492942</v>
@@ -544,7 +544,7 @@
         <v>1992</v>
       </c>
       <c r="B17">
-        <v>0.7594594124613165</v>
+        <v>0.7994767018260626</v>
       </c>
       <c r="C17">
         <v>0.492942</v>
@@ -555,7 +555,7 @@
         <v>1993</v>
       </c>
       <c r="B18">
-        <v>0.7799228759140893</v>
+        <v>0.800281793033125</v>
       </c>
       <c r="C18">
         <v>0.492942</v>
@@ -566,7 +566,7 @@
         <v>1994</v>
       </c>
       <c r="B19">
-        <v>0.7881432871604723</v>
+        <v>0.7983290564231738</v>
       </c>
       <c r="C19">
         <v>0.492942</v>
@@ -577,7 +577,7 @@
         <v>1995</v>
       </c>
       <c r="B20">
-        <v>0.7504218314441791</v>
+        <v>0.7736124301672795</v>
       </c>
       <c r="C20">
         <v>0.492942</v>
@@ -588,7 +588,7 @@
         <v>1996</v>
       </c>
       <c r="B21">
-        <v>0.7558704198910935</v>
+        <v>0.789183466332655</v>
       </c>
       <c r="C21">
         <v>0.492942</v>
@@ -599,7 +599,7 @@
         <v>1997</v>
       </c>
       <c r="B22">
-        <v>0.7261289654637684</v>
+        <v>0.7596596838519357</v>
       </c>
       <c r="C22">
         <v>0.492942</v>
@@ -610,7 +610,7 @@
         <v>1998</v>
       </c>
       <c r="B23">
-        <v>0.7255649235667551</v>
+        <v>0.7622286213939271</v>
       </c>
       <c r="C23">
         <v>0.492942</v>
@@ -621,7 +621,7 @@
         <v>1999</v>
       </c>
       <c r="B24">
-        <v>0.6672590720847671</v>
+        <v>0.7012780262249617</v>
       </c>
       <c r="C24">
         <v>0.492942</v>
@@ -632,7 +632,7 @@
         <v>2000</v>
       </c>
       <c r="B25">
-        <v>0.6616915710805069</v>
+        <v>0.6950846654472871</v>
       </c>
       <c r="C25">
         <v>0.492942</v>
@@ -643,7 +643,7 @@
         <v>2001</v>
       </c>
       <c r="B26">
-        <v>0.6918211432633512</v>
+        <v>0.7286139167241803</v>
       </c>
       <c r="C26">
         <v>0.492942</v>
@@ -654,7 +654,7 @@
         <v>2002</v>
       </c>
       <c r="B27">
-        <v>0.7324126954392047</v>
+        <v>0.7644856335756041</v>
       </c>
       <c r="C27">
         <v>0.492942</v>
@@ -665,7 +665,7 @@
         <v>2003</v>
       </c>
       <c r="B28">
-        <v>0.8352885547983013</v>
+        <v>0.8642303390768615</v>
       </c>
       <c r="C28">
         <v>0.492942</v>
@@ -676,7 +676,7 @@
         <v>2004</v>
       </c>
       <c r="B29">
-        <v>0.8617015110392654</v>
+        <v>0.8965056778071004</v>
       </c>
       <c r="C29">
         <v>0.492942</v>
@@ -687,7 +687,7 @@
         <v>2005</v>
       </c>
       <c r="B30">
-        <v>0.8686613912856289</v>
+        <v>0.911153260750166</v>
       </c>
       <c r="C30">
         <v>0.492942</v>
@@ -698,7 +698,7 @@
         <v>2006</v>
       </c>
       <c r="B31">
-        <v>0.7755561003814908</v>
+        <v>0.8176313250645968</v>
       </c>
       <c r="C31">
         <v>0.492942</v>
@@ -709,7 +709,7 @@
         <v>2007</v>
       </c>
       <c r="B32">
-        <v>0.7100022361171351</v>
+        <v>0.7522126768408604</v>
       </c>
       <c r="C32">
         <v>0.492942</v>
@@ -720,7 +720,7 @@
         <v>2008</v>
       </c>
       <c r="B33">
-        <v>0.6933696938983973</v>
+        <v>0.7338280360844065</v>
       </c>
       <c r="C33">
         <v>0.492942</v>
@@ -731,7 +731,7 @@
         <v>2009</v>
       </c>
       <c r="B34">
-        <v>0.6862038835983684</v>
+        <v>0.7187579276272675</v>
       </c>
       <c r="C34">
         <v>0.492942</v>
@@ -742,7 +742,7 @@
         <v>2010</v>
       </c>
       <c r="B35">
-        <v>0.7440572318200878</v>
+        <v>0.7882869561578465</v>
       </c>
       <c r="C35">
         <v>0.492942</v>
@@ -753,7 +753,7 @@
         <v>2011</v>
       </c>
       <c r="B36">
-        <v>0.6954419696588554</v>
+        <v>0.7388770286262876</v>
       </c>
       <c r="C36">
         <v>0.492942</v>
@@ -764,7 +764,7 @@
         <v>2012</v>
       </c>
       <c r="B37">
-        <v>0.6442700961351459</v>
+        <v>0.6923029251498252</v>
       </c>
       <c r="C37">
         <v>0.492942</v>
@@ -775,7 +775,7 @@
         <v>2013</v>
       </c>
       <c r="B38">
-        <v>0.5961678972730829</v>
+        <v>0.6396726800033123</v>
       </c>
       <c r="C38">
         <v>0.492942</v>
@@ -786,7 +786,7 @@
         <v>2014</v>
       </c>
       <c r="B39">
-        <v>0.5666895851419369</v>
+        <v>0.6095732565980103</v>
       </c>
       <c r="C39">
         <v>0.492942</v>
@@ -797,7 +797,7 @@
         <v>2015</v>
       </c>
       <c r="B40">
-        <v>0.6215436604262268</v>
+        <v>0.6736256801286941</v>
       </c>
       <c r="C40">
         <v>0.492942</v>
@@ -808,7 +808,7 @@
         <v>2016</v>
       </c>
       <c r="B41">
-        <v>0.6527455197701554</v>
+        <v>0.6999432524343596</v>
       </c>
       <c r="C41">
         <v>0.492942</v>
@@ -819,7 +819,7 @@
         <v>2017</v>
       </c>
       <c r="B42">
-        <v>0.651790650396957</v>
+        <v>0.6873375180872554</v>
       </c>
       <c r="C42">
         <v>0.492942</v>
@@ -830,7 +830,7 @@
         <v>2018</v>
       </c>
       <c r="B43">
-        <v>0.6468260629513092</v>
+        <v>0.6777789895512358</v>
       </c>
       <c r="C43">
         <v>0.492942</v>
@@ -841,7 +841,7 @@
         <v>2019</v>
       </c>
       <c r="B44">
-        <v>0.6451194452751847</v>
+        <v>0.6743862436107948</v>
       </c>
       <c r="C44">
         <v>0.492942</v>
@@ -852,7 +852,7 @@
         <v>2020</v>
       </c>
       <c r="B45">
-        <v>0.6168326010412801</v>
+        <v>0.6439595395041764</v>
       </c>
       <c r="C45">
         <v>0.492942</v>
@@ -863,7 +863,7 @@
         <v>2021</v>
       </c>
       <c r="B46">
-        <v>0.6241020927754963</v>
+        <v>0.6523613071938086</v>
       </c>
       <c r="C46">
         <v>0.492942</v>
@@ -874,7 +874,7 @@
         <v>2022</v>
       </c>
       <c r="B47">
-        <v>0.6756152978355653</v>
+        <v>0.7072381306740174</v>
       </c>
       <c r="C47">
         <v>0.492942</v>
@@ -885,7 +885,7 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>0.675656890162969</v>
+        <v>0.7066042951722435</v>
       </c>
       <c r="C48">
         <v>0.492942</v>
@@ -896,7 +896,7 @@
         <v>2024</v>
       </c>
       <c r="B49">
-        <v>0.6725222887713093</v>
+        <v>0.7037008383064589</v>
       </c>
       <c r="C49">
         <v>0.492942</v>
@@ -907,7 +907,7 @@
         <v>2025</v>
       </c>
       <c r="B50">
-        <v>0.6694732253316422</v>
+        <v>0.7021950750583411</v>
       </c>
       <c r="C50">
         <v>0.492942</v>
@@ -961,10 +961,10 @@
         <v>68375.58069949184</v>
       </c>
       <c r="D2">
-        <v>123453.376096715</v>
+        <v>135770.5402308904</v>
       </c>
       <c r="E2">
-        <v>52850.91533467436</v>
+        <v>57354.37746756569</v>
       </c>
     </row>
     <row r="3">
@@ -978,10 +978,10 @@
         <v>83775.94120782787</v>
       </c>
       <c r="D3">
-        <v>152458.707245448</v>
+        <v>167906.7454223806</v>
       </c>
       <c r="E3">
-        <v>65536.84331409552</v>
+        <v>70479.24762486508</v>
       </c>
     </row>
     <row r="4">
@@ -995,10 +995,10 @@
         <v>87517.25986196386</v>
       </c>
       <c r="D4">
-        <v>193610.7881161118</v>
+        <v>214497.8409565846</v>
       </c>
       <c r="E4">
-        <v>68405.83532874168</v>
+        <v>73427.02571891193</v>
       </c>
     </row>
     <row r="5">
@@ -1012,10 +1012,10 @@
         <v>91141.03506761891</v>
       </c>
       <c r="D5">
-        <v>245605.4321402864</v>
+        <v>271150.3407830977</v>
       </c>
       <c r="E5">
-        <v>70105.14896214393</v>
+        <v>75346.39937663675</v>
       </c>
     </row>
     <row r="6">
@@ -1029,10 +1029,10 @@
         <v>118189.9352754393</v>
       </c>
       <c r="D6">
-        <v>285430.6639260004</v>
+        <v>317787.5819474226</v>
       </c>
       <c r="E6">
-        <v>83016.77739171802</v>
+        <v>90780.48564586023</v>
       </c>
     </row>
     <row r="7">
@@ -1046,10 +1046,10 @@
         <v>167547.8018594395</v>
       </c>
       <c r="D7">
-        <v>332308.4891887475</v>
+        <v>372498.298739625</v>
       </c>
       <c r="E7">
-        <v>113822.5884027702</v>
+        <v>125259.0310492771</v>
       </c>
     </row>
     <row r="8">
@@ -1063,10 +1063,10 @@
         <v>207740.906764982</v>
       </c>
       <c r="D8">
-        <v>392122.28550243</v>
+        <v>440058.3145086519</v>
       </c>
       <c r="E8">
-        <v>139695.6639350592</v>
+        <v>154115.0667267796</v>
       </c>
     </row>
     <row r="9">
@@ -1080,10 +1080,10 @@
         <v>252457.4327605183</v>
       </c>
       <c r="D9">
-        <v>438984.6381660886</v>
+        <v>491901.8324639843</v>
       </c>
       <c r="E9">
-        <v>166408.9694800796</v>
+        <v>184498.423372854</v>
       </c>
     </row>
     <row r="10">
@@ -1097,10 +1097,10 @@
         <v>319723.1428735273</v>
       </c>
       <c r="D10">
-        <v>494643.5097955115</v>
+        <v>551271.1854074695</v>
       </c>
       <c r="E10">
-        <v>213948.7473759039</v>
+        <v>236130.6741022314</v>
       </c>
     </row>
     <row r="11">
@@ -1114,10 +1114,10 @@
         <v>381218.1476070861</v>
       </c>
       <c r="D11">
-        <v>566465.1575254014</v>
+        <v>626983.9871607375</v>
       </c>
       <c r="E11">
-        <v>264480.425644753</v>
+        <v>289198.8291315367</v>
       </c>
     </row>
     <row r="12">
@@ -1131,10 +1131,10 @@
         <v>413257.3777888571</v>
       </c>
       <c r="D12">
-        <v>631827.1056667196</v>
+        <v>694439.6822653956</v>
       </c>
       <c r="E12">
-        <v>295122.0387516835</v>
+        <v>320667.7864179966</v>
       </c>
     </row>
     <row r="13">
@@ -1148,10 +1148,10 @@
         <v>434121.3388751178</v>
       </c>
       <c r="D13">
-        <v>675502.4838552753</v>
+        <v>736971.1400538834</v>
       </c>
       <c r="E13">
-        <v>316631.4075348905</v>
+        <v>342419.6771055625</v>
       </c>
     </row>
     <row r="14">
@@ -1165,10 +1165,10 @@
         <v>472492.0568402593</v>
       </c>
       <c r="D14">
-        <v>707108.5305950048</v>
+        <v>766310.6658807173</v>
       </c>
       <c r="E14">
-        <v>354118.1866663951</v>
+        <v>380439.9923254342</v>
       </c>
     </row>
     <row r="15">
@@ -1182,10 +1182,10 @@
         <v>491124.6878920327</v>
       </c>
       <c r="D15">
-        <v>716548.2440173216</v>
+        <v>772013.9881760459</v>
       </c>
       <c r="E15">
-        <v>379051.3313060856</v>
+        <v>404481.4936075752</v>
       </c>
     </row>
     <row r="16">
@@ -1199,10 +1199,10 @@
         <v>466795.7130986929</v>
       </c>
       <c r="D16">
-        <v>694729.7842816157</v>
+        <v>747073.3579959839</v>
       </c>
       <c r="E16">
-        <v>366494.1373693832</v>
+        <v>389677.1652133766</v>
       </c>
     </row>
     <row r="17">
@@ -1216,10 +1216,10 @@
         <v>433093.5585982004</v>
       </c>
       <c r="D17">
-        <v>670908.8010834244</v>
+        <v>720182.9572413552</v>
       </c>
       <c r="E17">
-        <v>344822.3921494451</v>
+        <v>365664.8559939192</v>
       </c>
     </row>
     <row r="18">
@@ -1233,10 +1233,10 @@
         <v>397862.6648418929</v>
       </c>
       <c r="D18">
-        <v>639461.1988868817</v>
+        <v>684429.5758708686</v>
       </c>
       <c r="E18">
-        <v>319096.8343379032</v>
+        <v>338045.1246067664</v>
       </c>
     </row>
     <row r="19">
@@ -1250,10 +1250,10 @@
         <v>397400.0600327513</v>
       </c>
       <c r="D19">
-        <v>623103.647618031</v>
+        <v>663765.4208093347</v>
       </c>
       <c r="E19">
-        <v>323916.7538712264</v>
+        <v>341745.6952586963</v>
       </c>
     </row>
     <row r="20">
@@ -1267,10 +1267,10 @@
         <v>400246.6332443527</v>
       </c>
       <c r="D20">
-        <v>601374.4556151127</v>
+        <v>637564.7750267269</v>
       </c>
       <c r="E20">
-        <v>334106.6854439075</v>
+        <v>350422.1363825693</v>
       </c>
     </row>
     <row r="21">
@@ -1284,10 +1284,10 @@
         <v>365332.3560466953</v>
       </c>
       <c r="D21">
-        <v>554232.7971432594</v>
+        <v>586851.568012897</v>
       </c>
       <c r="E21">
-        <v>309749.1976607979</v>
+        <v>323737.2309204922</v>
       </c>
     </row>
     <row r="22">
@@ -1301,10 +1301,10 @@
         <v>322134.4907932275</v>
       </c>
       <c r="D22">
-        <v>513281.8105393018</v>
+        <v>542722.1702092472</v>
       </c>
       <c r="E22">
-        <v>276960.58625243</v>
+        <v>288517.734279686</v>
       </c>
     </row>
     <row r="23">
@@ -1318,10 +1318,10 @@
         <v>273598.2121637312</v>
       </c>
       <c r="D23">
-        <v>466149.9774324647</v>
+        <v>492632.8997671969</v>
       </c>
       <c r="E23">
-        <v>236554.3043527266</v>
+        <v>246182.4616486748</v>
       </c>
     </row>
     <row r="24">
@@ -1335,10 +1335,10 @@
         <v>244397.753735947</v>
       </c>
       <c r="D24">
-        <v>422932.3223102922</v>
+        <v>446186.0666466637</v>
       </c>
       <c r="E24">
-        <v>211351.2621731538</v>
+        <v>219870.9431770636</v>
       </c>
     </row>
     <row r="25">
@@ -1352,10 +1352,10 @@
         <v>214631.0707948864</v>
       </c>
       <c r="D25">
-        <v>372511.7348123892</v>
+        <v>393880.1127571674</v>
       </c>
       <c r="E25">
-        <v>183801.0467062579</v>
+        <v>191582.3354775863</v>
       </c>
     </row>
     <row r="26">
@@ -1369,10 +1369,10 @@
         <v>190726.8943128761</v>
       </c>
       <c r="D26">
-        <v>345618.3149605152</v>
+        <v>366308.0237111227</v>
       </c>
       <c r="E26">
-        <v>163109.3368610477</v>
+        <v>170038.9387771696</v>
       </c>
     </row>
     <row r="27">
@@ -1386,10 +1386,10 @@
         <v>175667.8344836868</v>
       </c>
       <c r="D27">
-        <v>337970.2120904999</v>
+        <v>356853.6659515231</v>
       </c>
       <c r="E27">
-        <v>151457.518002851</v>
+        <v>157513.9165713703</v>
       </c>
     </row>
     <row r="28">
@@ -1403,10 +1403,10 @@
         <v>164759.906594749</v>
       </c>
       <c r="D28">
-        <v>322831.8203327322</v>
+        <v>339480.3160954197</v>
       </c>
       <c r="E28">
-        <v>142403.2984699018</v>
+        <v>147922.6388363944</v>
       </c>
     </row>
     <row r="29">
@@ -1420,10 +1420,10 @@
         <v>163927.3563569855</v>
       </c>
       <c r="D29">
-        <v>300092.2725143235</v>
+        <v>314359.180758103</v>
       </c>
       <c r="E29">
-        <v>142600.2002623676</v>
+        <v>147810.5216688232</v>
       </c>
     </row>
     <row r="30">
@@ -1437,10 +1437,10 @@
         <v>152629.0716771489</v>
       </c>
       <c r="D30">
-        <v>267983.6452090585</v>
+        <v>280429.3834436564</v>
       </c>
       <c r="E30">
-        <v>134038.8786672072</v>
+        <v>138608.8374356842</v>
       </c>
     </row>
     <row r="31">
@@ -1454,10 +1454,10 @@
         <v>134372.1085380388</v>
       </c>
       <c r="D31">
-        <v>250896.2983301547</v>
+        <v>262780.2357351746</v>
       </c>
       <c r="E31">
-        <v>120040.4814328143</v>
+        <v>123653.1026286159</v>
       </c>
     </row>
     <row r="32">
@@ -1471,10 +1471,10 @@
         <v>110931.4713342069</v>
       </c>
       <c r="D32">
-        <v>256034.3489928366</v>
+        <v>269653.6026112069</v>
       </c>
       <c r="E32">
-        <v>100422.8634748468</v>
+        <v>103151.4203149344</v>
       </c>
     </row>
     <row r="33">
@@ -1488,10 +1488,10 @@
         <v>91410.09477526846</v>
       </c>
       <c r="D33">
-        <v>282456.4610806239</v>
+        <v>298196.9304174056</v>
       </c>
       <c r="E33">
-        <v>82739.04913130596</v>
+        <v>84974.88082946753</v>
       </c>
     </row>
     <row r="34">
@@ -1505,10 +1505,10 @@
         <v>90367.86806575903</v>
       </c>
       <c r="D34">
-        <v>318665.1932977583</v>
+        <v>335693.2913678385</v>
       </c>
       <c r="E34">
-        <v>80245.29926478156</v>
+        <v>82685.82388493069</v>
       </c>
     </row>
     <row r="35">
@@ -1522,10 +1522,10 @@
         <v>121541.2688044056</v>
       </c>
       <c r="D35">
-        <v>357907.1042009583</v>
+        <v>376373.6880755518</v>
       </c>
       <c r="E35">
-        <v>107800.5784328368</v>
+        <v>110979.1682742891</v>
       </c>
     </row>
     <row r="36">
@@ -1539,10 +1539,10 @@
         <v>140223.9919598005</v>
       </c>
       <c r="D36">
-        <v>351569.731279894</v>
+        <v>367276.6287590266</v>
       </c>
       <c r="E36">
-        <v>124296.8269924686</v>
+        <v>127952.5014283616</v>
       </c>
     </row>
     <row r="37">
@@ -1556,10 +1556,10 @@
         <v>143302.7501035137</v>
       </c>
       <c r="D37">
-        <v>322921.3421398885</v>
+        <v>337228.1351179836</v>
       </c>
       <c r="E37">
-        <v>126634.4982850318</v>
+        <v>130426.4314857083</v>
       </c>
     </row>
     <row r="38">
@@ -1573,10 +1573,10 @@
         <v>137754.060672575</v>
       </c>
       <c r="D38">
-        <v>299327.7111048182</v>
+        <v>313028.9329185439</v>
       </c>
       <c r="E38">
-        <v>122574.6505299416</v>
+        <v>126031.8130302043</v>
       </c>
     </row>
     <row r="39">
@@ -1590,10 +1590,10 @@
         <v>120972.6311053807</v>
       </c>
       <c r="D39">
-        <v>286722.798319069</v>
+        <v>300069.7670223874</v>
       </c>
       <c r="E39">
-        <v>108532.4601771811</v>
+        <v>111372.6141096139</v>
       </c>
     </row>
     <row r="40">
@@ -1607,10 +1607,10 @@
         <v>96639.70821922124</v>
       </c>
       <c r="D40">
-        <v>251535.9559142754</v>
+        <v>263964.8407813667</v>
       </c>
       <c r="E40">
-        <v>84869.17249923584</v>
+        <v>87507.11817262485</v>
       </c>
     </row>
     <row r="41">
@@ -1624,10 +1624,10 @@
         <v>92951.68242668931</v>
       </c>
       <c r="D41">
-        <v>207761.141450995</v>
+        <v>218737.5731792808</v>
       </c>
       <c r="E41">
-        <v>78471.99670319974</v>
+        <v>81654.53994057864</v>
       </c>
     </row>
     <row r="42">
@@ -1641,10 +1641,10 @@
         <v>93539.54266159181</v>
       </c>
       <c r="D42">
-        <v>164340.6924829663</v>
+        <v>174523.5901573441</v>
       </c>
       <c r="E42">
-        <v>76263.62365554855</v>
+        <v>80103.71667886645</v>
       </c>
     </row>
     <row r="43">
@@ -1658,10 +1658,10 @@
         <v>80091.84616234903</v>
       </c>
       <c r="D43">
-        <v>134018.1713197495</v>
+        <v>144496.8909966352</v>
       </c>
       <c r="E43">
-        <v>62621.59002320784</v>
+        <v>66633.07307553984</v>
       </c>
     </row>
     <row r="44">
@@ -1675,10 +1675,10 @@
         <v>77994.65849710979</v>
       </c>
       <c r="D44">
-        <v>145028.6542861808</v>
+        <v>156046.0883579192</v>
       </c>
       <c r="E44">
-        <v>62334.97572368169</v>
+        <v>66063.83592730723</v>
       </c>
     </row>
     <row r="45">
@@ -1692,10 +1692,10 @@
         <v>76644.99837004802</v>
       </c>
       <c r="D45">
-        <v>158512.1681653596</v>
+        <v>169518.1820172213</v>
       </c>
       <c r="E45">
-        <v>62083.14389359258</v>
+        <v>65614.42529840418</v>
       </c>
     </row>
     <row r="46">
@@ -1709,10 +1709,10 @@
         <v>91001.96258823808</v>
       </c>
       <c r="D46">
-        <v>180974.0245377118</v>
+        <v>191924.1843278405</v>
       </c>
       <c r="E46">
-        <v>76231.16771312035</v>
+        <v>79838.70388021709</v>
       </c>
     </row>
     <row r="47">
@@ -1726,10 +1726,10 @@
         <v>100896.1748708622</v>
       </c>
       <c r="D47">
-        <v>192626.0138058314</v>
+        <v>204068.1768958828</v>
       </c>
       <c r="E47">
-        <v>86036.12054651986</v>
+        <v>89735.50660635286</v>
       </c>
     </row>
     <row r="48">
@@ -1743,10 +1743,10 @@
         <v>100395.4279455645</v>
       </c>
       <c r="D48">
-        <v>198463.7089091204</v>
+        <v>210183.1217435077</v>
       </c>
       <c r="E48">
-        <v>86884.04314936523</v>
+        <v>90372.09922730731</v>
       </c>
     </row>
     <row r="49">
@@ -1760,10 +1760,10 @@
         <v>100901.0219219392</v>
       </c>
       <c r="D49">
-        <v>210210.8803300725</v>
+        <v>222298.5024967127</v>
       </c>
       <c r="E49">
-        <v>88983.81083721059</v>
+        <v>92263.64172752573</v>
       </c>
     </row>
     <row r="50">
@@ -1777,10 +1777,10 @@
         <v>104071.7271925989</v>
       </c>
       <c r="D50">
-        <v>219455.6515061877</v>
+        <v>232416.1245313651</v>
       </c>
       <c r="E50">
-        <v>93151.63439255896</v>
+        <v>96504.41071529423</v>
       </c>
     </row>
   </sheetData>
@@ -1810,7 +1810,7 @@
         <v>1977</v>
       </c>
       <c r="B2">
-        <v>958.9687544141135</v>
+        <v>1620.710113145166</v>
       </c>
     </row>
     <row r="3">
@@ -1818,7 +1818,7 @@
         <v>1978</v>
       </c>
       <c r="B3">
-        <v>2691.961019692406</v>
+        <v>4122.269088980998</v>
       </c>
     </row>
     <row r="4">
@@ -1826,7 +1826,7 @@
         <v>1979</v>
       </c>
       <c r="B4">
-        <v>2207.73947917075</v>
+        <v>4346.194345849378</v>
       </c>
     </row>
     <row r="5">
@@ -1834,7 +1834,7 @@
         <v>1980</v>
       </c>
       <c r="B5">
-        <v>1798.066520815665</v>
+        <v>3183.254778955983</v>
       </c>
     </row>
     <row r="6">
@@ -1842,7 +1842,7 @@
         <v>1981</v>
       </c>
       <c r="B6">
-        <v>2906.925603148202</v>
+        <v>4736.199668545914</v>
       </c>
     </row>
     <row r="7">
@@ -1850,7 +1850,7 @@
         <v>1982</v>
       </c>
       <c r="B7">
-        <v>2917.544978310828</v>
+        <v>4918.635778738599</v>
       </c>
     </row>
     <row r="8">
@@ -1858,7 +1858,7 @@
         <v>1983</v>
       </c>
       <c r="B8">
-        <v>3115.638293880506</v>
+        <v>5352.533964011603</v>
       </c>
     </row>
     <row r="9">
@@ -1866,7 +1866,7 @@
         <v>1984</v>
       </c>
       <c r="B9">
-        <v>2787.777100593783</v>
+        <v>4600.619606227348</v>
       </c>
     </row>
     <row r="10">
@@ -1874,7 +1874,7 @@
         <v>1985</v>
       </c>
       <c r="B10">
-        <v>3678.49498915656</v>
+        <v>5451.878577561776</v>
       </c>
     </row>
     <row r="11">
@@ -1882,7 +1882,7 @@
         <v>1986</v>
       </c>
       <c r="B11">
-        <v>4445.364416629639</v>
+        <v>6755.054340690981</v>
       </c>
     </row>
     <row r="12">
@@ -1890,7 +1890,7 @@
         <v>1987</v>
       </c>
       <c r="B12">
-        <v>3929.042228723316</v>
+        <v>6350.705491121706</v>
       </c>
     </row>
     <row r="13">
@@ -1898,7 +1898,7 @@
         <v>1988</v>
       </c>
       <c r="B13">
-        <v>3866.83466782426</v>
+        <v>5868.126567757719</v>
       </c>
     </row>
     <row r="14">
@@ -1906,7 +1906,7 @@
         <v>1989</v>
       </c>
       <c r="B14">
-        <v>3747.007338246302</v>
+        <v>6058.768503402744</v>
       </c>
     </row>
     <row r="15">
@@ -1914,7 +1914,7 @@
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>4363.294242110647</v>
+        <v>6757.77670911275</v>
       </c>
     </row>
     <row r="16">
@@ -1922,7 +1922,7 @@
         <v>1991</v>
       </c>
       <c r="B16">
-        <v>5813.816384109096</v>
+        <v>8556.029237287345</v>
       </c>
     </row>
     <row r="17">
@@ -1930,7 +1930,7 @@
         <v>1992</v>
       </c>
       <c r="B17">
-        <v>5907.443986823646</v>
+        <v>8617.720495413832</v>
       </c>
     </row>
     <row r="18">
@@ -1938,7 +1938,7 @@
         <v>1993</v>
       </c>
       <c r="B18">
-        <v>5472.069622675082</v>
+        <v>7248.762758866522</v>
       </c>
     </row>
     <row r="19">
@@ -1946,7 +1946,7 @@
         <v>1994</v>
       </c>
       <c r="B19">
-        <v>5095.277714796276</v>
+        <v>6642.136842428359</v>
       </c>
     </row>
     <row r="20">
@@ -1954,7 +1954,7 @@
         <v>1995</v>
       </c>
       <c r="B20">
-        <v>4627.505706520315</v>
+        <v>6420.060275880052</v>
       </c>
     </row>
     <row r="21">
@@ -1962,7 +1962,7 @@
         <v>1996</v>
       </c>
       <c r="B21">
-        <v>5605.336130228024</v>
+        <v>8001.66797848764</v>
       </c>
     </row>
     <row r="22">
@@ -1970,7 +1970,7 @@
         <v>1997</v>
       </c>
       <c r="B22">
-        <v>4799.223866895441</v>
+        <v>7262.580136599579</v>
       </c>
     </row>
     <row r="23">
@@ -1978,7 +1978,7 @@
         <v>1998</v>
       </c>
       <c r="B23">
-        <v>3954.948586807308</v>
+        <v>6393.815076742412</v>
       </c>
     </row>
     <row r="24">
@@ -1986,7 +1986,7 @@
         <v>1999</v>
       </c>
       <c r="B24">
-        <v>2772.934427436239</v>
+        <v>4707.526407868019</v>
       </c>
     </row>
     <row r="25">
@@ -1994,7 +1994,7 @@
         <v>2000</v>
       </c>
       <c r="B25">
-        <v>3192.061414604505</v>
+        <v>5135.269344098213</v>
       </c>
     </row>
     <row r="26">
@@ -2002,7 +2002,7 @@
         <v>2001</v>
       </c>
       <c r="B26">
-        <v>3517.502112791858</v>
+        <v>5959.113623493216</v>
       </c>
     </row>
     <row r="27">
@@ -2010,7 +2010,7 @@
         <v>2002</v>
       </c>
       <c r="B27">
-        <v>2816.087589576238</v>
+        <v>4693.320688865674</v>
       </c>
     </row>
     <row r="28">
@@ -2018,7 +2018,7 @@
         <v>2003</v>
       </c>
       <c r="B28">
-        <v>3050.3743664637</v>
+        <v>4459.716030416209</v>
       </c>
     </row>
     <row r="29">
@@ -2026,7 +2026,7 @@
         <v>2004</v>
       </c>
       <c r="B29">
-        <v>3097.621420252041</v>
+        <v>4270.487083815096</v>
       </c>
     </row>
     <row r="30">
@@ -2034,7 +2034,7 @@
         <v>2005</v>
       </c>
       <c r="B30">
-        <v>3912.894756358517</v>
+        <v>5248.856128121321</v>
       </c>
     </row>
     <row r="31">
@@ -2042,7 +2042,7 @@
         <v>2006</v>
       </c>
       <c r="B31">
-        <v>5041.250718945676</v>
+        <v>6711.864997153926</v>
       </c>
     </row>
     <row r="32">
@@ -2050,7 +2050,7 @@
         <v>2007</v>
       </c>
       <c r="B32">
-        <v>6323.252927812684</v>
+        <v>8780.353934953177</v>
       </c>
     </row>
     <row r="33">
@@ -2058,7 +2058,7 @@
         <v>2008</v>
       </c>
       <c r="B33">
-        <v>5339.118866178153</v>
+        <v>8315.071609144668</v>
       </c>
     </row>
     <row r="34">
@@ -2066,7 +2066,7 @@
         <v>2009</v>
       </c>
       <c r="B34">
-        <v>5052.747742376025</v>
+        <v>7433.058265784439</v>
       </c>
     </row>
     <row r="35">
@@ -2074,7 +2074,7 @@
         <v>2010</v>
       </c>
       <c r="B35">
-        <v>3882.633017132572</v>
+        <v>7312.74484733071</v>
       </c>
     </row>
     <row r="36">
@@ -2082,7 +2082,7 @@
         <v>2011</v>
       </c>
       <c r="B36">
-        <v>2848.869174927039</v>
+        <v>4764.138109340156</v>
       </c>
     </row>
     <row r="37">
@@ -2090,7 +2090,7 @@
         <v>2012</v>
       </c>
       <c r="B37">
-        <v>2713.62164009188</v>
+        <v>4554.303029564172</v>
       </c>
     </row>
     <row r="38">
@@ -2098,7 +2098,7 @@
         <v>2013</v>
       </c>
       <c r="B38">
-        <v>2639.506234386302</v>
+        <v>4512.920995596941</v>
       </c>
     </row>
     <row r="39">
@@ -2106,7 +2106,7 @@
         <v>2014</v>
       </c>
       <c r="B39">
-        <v>1497.594158612404</v>
+        <v>2990.994567710714</v>
       </c>
     </row>
     <row r="40">
@@ -2114,7 +2114,7 @@
         <v>2015</v>
       </c>
       <c r="B40">
-        <v>961.3643020470674</v>
+        <v>1975.324517888298</v>
       </c>
     </row>
     <row r="41">
@@ -2122,7 +2122,7 @@
         <v>2016</v>
       </c>
       <c r="B41">
-        <v>733.1398658599021</v>
+        <v>1293.912077760237</v>
       </c>
     </row>
     <row r="42">
@@ -2130,7 +2130,7 @@
         <v>2017</v>
       </c>
       <c r="B42">
-        <v>1080.676511275825</v>
+        <v>1651.26292846648</v>
       </c>
     </row>
     <row r="43">
@@ -2138,7 +2138,7 @@
         <v>2018</v>
       </c>
       <c r="B43">
-        <v>1476.136391274179</v>
+        <v>2322.700894558359</v>
       </c>
     </row>
     <row r="44">
@@ -2146,7 +2146,7 @@
         <v>2019</v>
       </c>
       <c r="B44">
-        <v>1656.803393832253</v>
+        <v>2635.210832976051</v>
       </c>
     </row>
     <row r="45">
@@ -2154,7 +2154,7 @@
         <v>2020</v>
       </c>
       <c r="B45">
-        <v>1176.577863732073</v>
+        <v>1860.883964411844</v>
       </c>
     </row>
     <row r="46">
@@ -2162,7 +2162,7 @@
         <v>2021</v>
       </c>
       <c r="B46">
-        <v>1376.22619531371</v>
+        <v>1959.348227681465</v>
       </c>
     </row>
     <row r="47">
@@ -2170,7 +2170,7 @@
         <v>2022</v>
       </c>
       <c r="B47">
-        <v>2058.431907494391</v>
+        <v>2990.189764770932</v>
       </c>
     </row>
     <row r="48">
@@ -2178,7 +2178,7 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>1904.086454399429</v>
+        <v>2910.676374499609</v>
       </c>
     </row>
     <row r="49">
@@ -2186,7 +2186,7 @@
         <v>2024</v>
       </c>
       <c r="B49">
-        <v>2059.531184796147</v>
+        <v>3064.785986557903</v>
       </c>
     </row>
     <row r="50">
@@ -2194,7 +2194,7 @@
         <v>2025</v>
       </c>
       <c r="B50">
-        <v>2220.472208980446</v>
+        <v>3353.911796926472</v>
       </c>
     </row>
   </sheetData>
@@ -2229,10 +2229,10 @@
         <v>1977</v>
       </c>
       <c r="B2">
-        <v>104134.5525149916</v>
+        <v>112621.7339050821</v>
       </c>
       <c r="C2">
-        <v>156307.3725890305</v>
+        <v>170812.606999367</v>
       </c>
     </row>
     <row r="3">
@@ -2240,10 +2240,10 @@
         <v>1978</v>
       </c>
       <c r="B3">
-        <v>122739.1710480768</v>
+        <v>131992.7539068172</v>
       </c>
       <c r="C3">
-        <v>192283.8665324071</v>
+        <v>211337.488627237</v>
       </c>
     </row>
     <row r="4">
@@ -2251,10 +2251,10 @@
         <v>1979</v>
       </c>
       <c r="B4">
-        <v>113273.928729621</v>
+        <v>121548.9208247385</v>
       </c>
       <c r="C4">
-        <v>250309.5452246538</v>
+        <v>276057.5640646127</v>
       </c>
     </row>
     <row r="5">
@@ -2262,10 +2262,10 @@
         <v>1980</v>
       </c>
       <c r="B5">
-        <v>111940.6216387978</v>
+        <v>121080.9664645821</v>
       </c>
       <c r="C5">
-        <v>305073.8027009263</v>
+        <v>337131.8939219169</v>
       </c>
     </row>
     <row r="6">
@@ -2273,10 +2273,10 @@
         <v>1981</v>
       </c>
       <c r="B6">
-        <v>237400.0345085331</v>
+        <v>260061.011214648</v>
       </c>
       <c r="C6">
-        <v>388259.108029335</v>
+        <v>432282.5458014894</v>
       </c>
     </row>
     <row r="7">
@@ -2284,10 +2284,10 @@
         <v>1982</v>
       </c>
       <c r="B7">
-        <v>218729.5824694092</v>
+        <v>240601.869279286</v>
       </c>
       <c r="C7">
-        <v>391343.135076751</v>
+        <v>437846.6601707307</v>
       </c>
     </row>
     <row r="8">
@@ -2295,10 +2295,10 @@
         <v>1983</v>
       </c>
       <c r="B8">
-        <v>276465.7776824433</v>
+        <v>305352.4721932827</v>
       </c>
       <c r="C8">
-        <v>504358.1296089365</v>
+        <v>564850.67084272</v>
       </c>
     </row>
     <row r="9">
@@ -2306,10 +2306,10 @@
         <v>1984</v>
       </c>
       <c r="B9">
-        <v>352833.8441962747</v>
+        <v>390383.5986923757</v>
       </c>
       <c r="C9">
-        <v>554588.9066754566</v>
+        <v>618780.7595828029</v>
       </c>
     </row>
     <row r="10">
@@ -2317,10 +2317,10 @@
         <v>1985</v>
       </c>
       <c r="B10">
-        <v>433484.2758251461</v>
+        <v>476075.4318400346</v>
       </c>
       <c r="C10">
-        <v>622063.7466701154</v>
+        <v>689511.6636595782</v>
       </c>
     </row>
     <row r="11">
@@ -2328,10 +2328,10 @@
         <v>1986</v>
       </c>
       <c r="B11">
-        <v>487291.4829182797</v>
+        <v>531434.6711650314</v>
       </c>
       <c r="C11">
-        <v>713986.4344509016</v>
+        <v>786417.7018574626</v>
       </c>
     </row>
     <row r="12">
@@ -2339,10 +2339,10 @@
         <v>1987</v>
       </c>
       <c r="B12">
-        <v>529220.57065344</v>
+        <v>574294.6782255206</v>
       </c>
       <c r="C12">
-        <v>824367.5834833947</v>
+        <v>901817.1763976243</v>
       </c>
     </row>
     <row r="13">
@@ -2350,10 +2350,10 @@
         <v>1988</v>
       </c>
       <c r="B13">
-        <v>576590.220831506</v>
+        <v>622184.4591001546</v>
       </c>
       <c r="C13">
-        <v>834293.6707840753</v>
+        <v>906020.5916423771</v>
       </c>
     </row>
     <row r="14">
@@ -2361,10 +2361,10 @@
         <v>1989</v>
       </c>
       <c r="B14">
-        <v>612479.3013568564</v>
+        <v>656053.219181806</v>
       </c>
       <c r="C14">
-        <v>815017.9218289607</v>
+        <v>879315.5802043393</v>
       </c>
     </row>
     <row r="15">
@@ -2372,10 +2372,10 @@
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>589165.5757666521</v>
+        <v>627785.9754397281</v>
       </c>
       <c r="C15">
-        <v>807906.8043009307</v>
+        <v>867869.6437423328</v>
       </c>
     </row>
     <row r="16">
@@ -2383,10 +2383,10 @@
         <v>1991</v>
       </c>
       <c r="B16">
-        <v>589142.6886263913</v>
+        <v>625569.1827212683</v>
       </c>
       <c r="C16">
-        <v>800658.6099843748</v>
+        <v>858710.417810856</v>
       </c>
     </row>
     <row r="17">
@@ -2394,10 +2394,10 @@
         <v>1992</v>
       </c>
       <c r="B17">
-        <v>563116.8893854044</v>
+        <v>597034.8254000203</v>
       </c>
       <c r="C17">
-        <v>804897.6934037891</v>
+        <v>861833.9173336331</v>
       </c>
     </row>
     <row r="18">
@@ -2405,10 +2405,10 @@
         <v>1993</v>
       </c>
       <c r="B18">
-        <v>529552.9425449015</v>
+        <v>560111.5148282797</v>
       </c>
       <c r="C18">
-        <v>754186.335881222</v>
+        <v>804363.2696313866</v>
       </c>
     </row>
     <row r="19">
@@ -2416,10 +2416,10 @@
         <v>1994</v>
       </c>
       <c r="B19">
-        <v>565523.098127569</v>
+        <v>595508.3750678329</v>
       </c>
       <c r="C19">
-        <v>735406.6033886751</v>
+        <v>780225.3333371793</v>
       </c>
     </row>
     <row r="20">
@@ -2427,10 +2427,10 @@
         <v>1995</v>
       </c>
       <c r="B20">
-        <v>514278.8820558098</v>
+        <v>539063.3293790378</v>
       </c>
       <c r="C20">
-        <v>663668.7935554113</v>
+        <v>701536.6814637411</v>
       </c>
     </row>
     <row r="21">
@@ -2438,10 +2438,10 @@
         <v>1996</v>
       </c>
       <c r="B21">
-        <v>481571.6716257796</v>
+        <v>503105.1367101395</v>
       </c>
       <c r="C21">
-        <v>635930.4856650754</v>
+        <v>671369.0766976627</v>
       </c>
     </row>
     <row r="22">
@@ -2449,10 +2449,10 @@
         <v>1997</v>
       </c>
       <c r="B22">
-        <v>414808.5060431225</v>
+        <v>432279.0080228926</v>
       </c>
       <c r="C22">
-        <v>583646.8550427158</v>
+        <v>615675.7615916263</v>
       </c>
     </row>
     <row r="23">
@@ -2460,10 +2460,10 @@
         <v>1998</v>
       </c>
       <c r="B23">
-        <v>407875.4985741221</v>
+        <v>424795.4357582417</v>
       </c>
       <c r="C23">
-        <v>588380.7835311928</v>
+        <v>620187.7280693771</v>
       </c>
     </row>
     <row r="24">
@@ -2471,10 +2471,10 @@
         <v>1999</v>
       </c>
       <c r="B24">
-        <v>340086.9303868429</v>
+        <v>354407.0528356478</v>
       </c>
       <c r="C24">
-        <v>466599.3079156019</v>
+        <v>491640.5013949042</v>
       </c>
     </row>
     <row r="25">
@@ -2482,10 +2482,10 @@
         <v>2000</v>
       </c>
       <c r="B25">
-        <v>299133.77454786</v>
+        <v>311973.1723645877</v>
       </c>
       <c r="C25">
-        <v>420720.9766128066</v>
+        <v>444127.3201213417</v>
       </c>
     </row>
     <row r="26">
@@ -2493,10 +2493,10 @@
         <v>2001</v>
       </c>
       <c r="B26">
-        <v>279625.4263889897</v>
+        <v>291223.7426195793</v>
       </c>
       <c r="C26">
-        <v>417620.7314096555</v>
+        <v>441051.9252862903</v>
       </c>
     </row>
     <row r="27">
@@ -2504,10 +2504,10 @@
         <v>2002</v>
       </c>
       <c r="B27">
-        <v>236957.3937948454</v>
+        <v>246253.3086497746</v>
       </c>
       <c r="C27">
-        <v>376766.4332998166</v>
+        <v>396525.614043223</v>
       </c>
     </row>
     <row r="28">
@@ -2515,10 +2515,10 @@
         <v>2003</v>
       </c>
       <c r="B28">
-        <v>270993.5218235647</v>
+        <v>281326.5109682599</v>
       </c>
       <c r="C28">
-        <v>397551.4181783332</v>
+        <v>416677.1512820434</v>
       </c>
     </row>
     <row r="29">
@@ -2526,10 +2526,10 @@
         <v>2004</v>
       </c>
       <c r="B29">
-        <v>254882.9247013658</v>
+        <v>264023.6888974994</v>
       </c>
       <c r="C29">
-        <v>340958.724643992</v>
+        <v>356221.643095149</v>
       </c>
     </row>
     <row r="30">
@@ -2537,10 +2537,10 @@
         <v>2005</v>
       </c>
       <c r="B30">
-        <v>228424.5716707645</v>
+        <v>235833.9622320346</v>
       </c>
       <c r="C30">
-        <v>313816.4093819049</v>
+        <v>327344.597660823</v>
       </c>
     </row>
     <row r="31">
@@ -2548,10 +2548,10 @@
         <v>2006</v>
       </c>
       <c r="B31">
-        <v>187991.3593872076</v>
+        <v>193457.0151837295</v>
       </c>
       <c r="C31">
-        <v>286558.3265620955</v>
+        <v>299401.3857582158</v>
       </c>
     </row>
     <row r="32">
@@ -2559,10 +2559,10 @@
         <v>2007</v>
       </c>
       <c r="B32">
-        <v>145260.7607073284</v>
+        <v>149176.5065191538</v>
       </c>
       <c r="C32">
-        <v>283202.9243566759</v>
+        <v>297621.814213977</v>
       </c>
     </row>
     <row r="33">
@@ -2570,10 +2570,10 @@
         <v>2008</v>
       </c>
       <c r="B33">
-        <v>129724.1837780683</v>
+        <v>133333.7333088225</v>
       </c>
       <c r="C33">
-        <v>321589.1809949231</v>
+        <v>338301.3485162052</v>
       </c>
     </row>
     <row r="34">
@@ -2581,10 +2581,10 @@
         <v>2009</v>
       </c>
       <c r="B34">
-        <v>156131.7452650518</v>
+        <v>160706.2091062359</v>
       </c>
       <c r="C34">
-        <v>351084.724514499</v>
+        <v>368503.4992870996</v>
       </c>
     </row>
     <row r="35">
@@ -2592,10 +2592,10 @@
         <v>2010</v>
       </c>
       <c r="B35">
-        <v>253642.4394875036</v>
+        <v>261079.1322688532</v>
       </c>
       <c r="C35">
-        <v>438458.7821362952</v>
+        <v>459069.0552825663</v>
       </c>
     </row>
     <row r="36">
@@ -2603,10 +2603,10 @@
         <v>2011</v>
       </c>
       <c r="B36">
-        <v>232457.7449047212</v>
+        <v>239325.6252493148</v>
       </c>
       <c r="C36">
-        <v>392751.2615663867</v>
+        <v>409359.7019771472</v>
       </c>
     </row>
     <row r="37">
@@ -2614,10 +2614,10 @@
         <v>2012</v>
       </c>
       <c r="B37">
-        <v>240034.8654866435</v>
+        <v>247033.5021874091</v>
       </c>
       <c r="C37">
-        <v>344603.5757334184</v>
+        <v>359057.8447632593</v>
       </c>
     </row>
     <row r="38">
@@ -2625,10 +2625,10 @@
         <v>2013</v>
       </c>
       <c r="B38">
-        <v>199206.1377414824</v>
+        <v>204549.7476115053</v>
       </c>
       <c r="C38">
-        <v>326349.7135654368</v>
+        <v>340569.9721600257</v>
       </c>
     </row>
     <row r="39">
@@ -2636,10 +2636,10 @@
         <v>2014</v>
       </c>
       <c r="B39">
-        <v>169489.1207514885</v>
+        <v>174148.9971854961</v>
       </c>
       <c r="C39">
-        <v>314297.0211106346</v>
+        <v>329008.7580275233</v>
       </c>
     </row>
     <row r="40">
@@ -2647,10 +2647,10 @@
         <v>2015</v>
       </c>
       <c r="B40">
-        <v>166458.1080827868</v>
+        <v>172128.430931183</v>
       </c>
       <c r="C40">
-        <v>302282.6784972339</v>
+        <v>317500.353229177</v>
       </c>
     </row>
     <row r="41">
@@ -2658,10 +2658,10 @@
         <v>2016</v>
       </c>
       <c r="B41">
-        <v>183112.9513727978</v>
+        <v>191338.37227471</v>
       </c>
       <c r="C41">
-        <v>247233.5717936106</v>
+        <v>260868.9457419494</v>
       </c>
     </row>
     <row r="42">
@@ -2669,10 +2669,10 @@
         <v>2017</v>
       </c>
       <c r="B42">
-        <v>138852.9104041859</v>
+        <v>146686.2801316914</v>
       </c>
       <c r="C42">
-        <v>178820.8112943319</v>
+        <v>190754.454629735</v>
       </c>
     </row>
     <row r="43">
@@ -2680,10 +2680,10 @@
         <v>2018</v>
       </c>
       <c r="B43">
-        <v>113723.6955286334</v>
+        <v>120664.591259586</v>
       </c>
       <c r="C43">
-        <v>169197.3665577556</v>
+        <v>181791.3391912982</v>
       </c>
     </row>
     <row r="44">
@@ -2691,10 +2691,10 @@
         <v>2019</v>
       </c>
       <c r="B44">
-        <v>113579.3282096663</v>
+        <v>120145.5628721903</v>
       </c>
       <c r="C44">
-        <v>197362.665475976</v>
+        <v>211481.0743852407</v>
       </c>
     </row>
     <row r="45">
@@ -2702,10 +2702,10 @@
         <v>2020</v>
       </c>
       <c r="B45">
-        <v>114250.8996519885</v>
+        <v>120120.777928459</v>
       </c>
       <c r="C45">
-        <v>192699.6596774861</v>
+        <v>204809.0148032242</v>
       </c>
     </row>
     <row r="46">
@@ -2713,10 +2713,10 @@
         <v>2021</v>
       </c>
       <c r="B46">
-        <v>139871.4393227159</v>
+        <v>146251.6088383607</v>
       </c>
       <c r="C46">
-        <v>211665.6997452844</v>
+        <v>223689.5591144678</v>
       </c>
     </row>
     <row r="47">
@@ -2724,10 +2724,10 @@
         <v>2022</v>
       </c>
       <c r="B47">
-        <v>164686.0853647432</v>
+        <v>171676.0663901008</v>
       </c>
       <c r="C47">
-        <v>239692.8754463358</v>
+        <v>253202.0444926934</v>
       </c>
     </row>
     <row r="48">
@@ -2735,10 +2735,10 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>143767.18566002</v>
+        <v>149250.1980394292</v>
       </c>
       <c r="C48">
-        <v>234727.9001282548</v>
+        <v>247633.2480686929</v>
       </c>
     </row>
     <row r="49">
@@ -2746,10 +2746,10 @@
         <v>2024</v>
       </c>
       <c r="B49">
-        <v>160129.7041176843</v>
+        <v>166138.1952418491</v>
       </c>
       <c r="C49">
-        <v>253477.9186428221</v>
+        <v>267266.8527734487</v>
       </c>
     </row>
     <row r="50">
@@ -2757,10 +2757,10 @@
         <v>2025</v>
       </c>
       <c r="B50">
-        <v>170646.9782041942</v>
+        <v>177089.3396480381</v>
       </c>
       <c r="C50">
-        <v>262051.4215312043</v>
+        <v>276974.5115231749</v>
       </c>
     </row>
   </sheetData>
